--- a/04_Outputs/rC_k600.xlsx
+++ b/04_Outputs/rC_k600.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -27,13 +27,16 @@
     <t xml:space="preserve">u</t>
   </si>
   <si>
+    <t xml:space="preserve">velocity</t>
+  </si>
+  <si>
     <t xml:space="preserve">ID</t>
   </si>
   <si>
     <t xml:space="preserve">uh</t>
   </si>
   <si>
-    <t xml:space="preserve">k600_1d</t>
+    <t xml:space="preserve">k600_1.day</t>
   </si>
   <si>
     <t xml:space="preserve">VentDO</t>
@@ -69,6 +72,9 @@
     <t xml:space="preserve">5/29/2023</t>
   </si>
   <si>
+    <t xml:space="preserve">11/7/2022</t>
+  </si>
+  <si>
     <t xml:space="preserve">11/21/2022</t>
   </si>
   <si>
@@ -142,6 +148,9 @@
   </si>
   <si>
     <t xml:space="preserve">OS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/20/2023</t>
   </si>
 </sst>
 </file>
@@ -495,10 +504,13 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="n">
         <v>0.663602771362776</v>
@@ -506,25 +518,28 @@
       <c r="C2" t="n">
         <v>0.41148</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" t="n">
+        <v>0.369728561140081</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.620069743161234</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>8.70001793557825</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1.5</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>71.99254</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
         <v>0.663602771362776</v>
@@ -532,25 +547,28 @@
       <c r="C3" t="n">
         <v>0.41148</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="D3" t="n">
+        <v>0.369728561140081</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.620069743161234</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>14.0537866274825</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1.5</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>71.99254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="n">
         <v>0.844965688329578</v>
@@ -558,25 +576,28 @@
       <c r="C4" t="n">
         <v>0.41148</v>
       </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4" t="n">
+        <v>0.316142515534118</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.486978353894416</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>14.2509884099436</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1.097</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>71.48696</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="n">
         <v>0.844965688329578</v>
@@ -584,25 +605,28 @@
       <c r="C5" t="n">
         <v>0.41148</v>
       </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" t="n">
+        <v>0.316142515534118</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.486978353894416</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>14.0195480980259</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1.097</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>71.48696</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
         <v>0.844965688329578</v>
@@ -610,25 +634,28 @@
       <c r="C6" t="n">
         <v>0.41148</v>
       </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6" t="n">
+        <v>0.316142515534118</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.486978353894416</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>17.9748429691486</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1.097</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>71.48696</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
         <v>1.79712100240526</v>
@@ -636,23 +663,26 @@
       <c r="C7" t="n">
         <v>0.096864407</v>
       </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" t="n">
+        <v>0.0348157761028232</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.0538997690585983</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>1.36597472936285</v>
       </c>
-      <c r="G7"/>
-      <c r="H7" t="n">
+      <c r="H7"/>
+      <c r="I7" t="n">
         <v>71.14078431</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="n">
         <v>1.79712100240526</v>
@@ -660,23 +690,26 @@
       <c r="C8" t="n">
         <v>0.096864407</v>
       </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8" t="n">
+        <v>0.0348157761028232</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
         <v>0.0538997690585983</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>1.43477614979118</v>
       </c>
-      <c r="G8"/>
-      <c r="H8" t="n">
+      <c r="H8"/>
+      <c r="I8" t="n">
         <v>71.14078431</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="n">
         <v>1.91936208989603</v>
@@ -684,25 +717,28 @@
       <c r="C9" t="n">
         <v>0.025907668</v>
       </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9" t="n">
+        <v>-0.00130195181397141</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.0134980617447766</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0.762817767337299</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1.288</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>71.42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n">
         <v>1.91936208989603</v>
@@ -710,25 +746,28 @@
       <c r="C10" t="n">
         <v>0.025907668</v>
       </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10" t="n">
+        <v>-0.00130195181397141</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.0134980617447766</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.954970513126703</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>1.288</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>71.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
         <v>1.53641180926549</v>
@@ -736,23 +775,26 @@
       <c r="C11" t="n">
         <v>0.111489093</v>
       </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11" t="n">
+        <v>0.111845716661391</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.0725645899931604</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>3.25318360355363</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1.26</v>
       </c>
-      <c r="H11"/>
+      <c r="I11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n">
         <v>1.53641180926549</v>
@@ -760,23 +802,26 @@
       <c r="C12" t="n">
         <v>0.111489093</v>
       </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12" t="n">
+        <v>0.111845716661391</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
         <v>0.0725645899931604</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>2.4433323290318</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>1.26</v>
       </c>
-      <c r="H12"/>
+      <c r="I12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" t="n">
         <v>1.53641180926549</v>
@@ -784,23 +829,26 @@
       <c r="C13" t="n">
         <v>0.111489093</v>
       </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="D13" t="n">
+        <v>0.111845716661391</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
         <v>0.0725645899931604</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>2.43040464475121</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>1.26</v>
       </c>
-      <c r="H13"/>
+      <c r="I13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" t="n">
         <v>1.14254792657094</v>
@@ -808,23 +856,26 @@
       <c r="C14" t="n">
         <v>0.081843182</v>
       </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14" t="n">
+        <v>0.228217951590072</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
         <v>0.071632165353125</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>7.04329706934836</v>
       </c>
-      <c r="G14"/>
-      <c r="H14" t="n">
+      <c r="H14"/>
+      <c r="I14" t="n">
         <v>72.60454545</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="n">
         <v>1.14254792657094</v>
@@ -832,23 +883,26 @@
       <c r="C15" t="n">
         <v>0.081843182</v>
       </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15" t="n">
+        <v>0.228217951590072</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
         <v>0.071632165353125</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>2.78398493321431</v>
       </c>
-      <c r="G15"/>
-      <c r="H15" t="n">
+      <c r="H15"/>
+      <c r="I15" t="n">
         <v>72.60454545</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="n">
         <v>1.14254792657094</v>
@@ -856,23 +910,26 @@
       <c r="C16" t="n">
         <v>0.081843182</v>
       </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="D16" t="n">
+        <v>0.228217951590072</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
         <v>0.071632165353125</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>2.78929180498941</v>
       </c>
-      <c r="G16"/>
-      <c r="H16" t="n">
+      <c r="H16"/>
+      <c r="I16" t="n">
         <v>72.60454545</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="n">
         <v>0.769489024446584</v>
@@ -880,17 +937,20 @@
       <c r="C17" t="n">
         <v>0.24384</v>
       </c>
-      <c r="D17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17" t="n">
+        <v>0.338443082930486</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
         <v>0.316885611429441</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>7.67547333558373</v>
       </c>
-      <c r="G17"/>
-      <c r="H17" t="n">
+      <c r="H17"/>
+      <c r="I17" t="n">
         <v>73.47818182</v>
       </c>
     </row>
@@ -900,15 +960,18 @@
         <v>0.746831987365931</v>
       </c>
       <c r="C18"/>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18"/>
-      <c r="F18" t="n">
+      <c r="D18" t="n">
+        <v>0.345137400835188</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18"/>
+      <c r="G18" t="n">
         <v>22.6241958580754</v>
       </c>
-      <c r="G18"/>
       <c r="H18"/>
+      <c r="I18"/>
     </row>
     <row r="19">
       <c r="A19"/>
@@ -916,15 +979,18 @@
         <v>0.746831987365931</v>
       </c>
       <c r="C19"/>
-      <c r="D19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19"/>
-      <c r="F19" t="n">
+      <c r="D19" t="n">
+        <v>0.345137400835188</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19"/>
+      <c r="G19" t="n">
         <v>22.5657731444328</v>
       </c>
-      <c r="G19"/>
       <c r="H19"/>
+      <c r="I19"/>
     </row>
     <row r="20">
       <c r="A20"/>
@@ -932,19 +998,22 @@
         <v>0.634197514012805</v>
       </c>
       <c r="C20"/>
-      <c r="D20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20"/>
-      <c r="F20" t="n">
+      <c r="D20" t="n">
+        <v>0.378416728973746</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20" t="n">
         <v>16.1504080056141</v>
       </c>
-      <c r="G20"/>
       <c r="H20"/>
+      <c r="I20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B21" t="n">
         <v>0.811937246128919</v>
@@ -952,21 +1021,24 @@
       <c r="C21" t="n">
         <v>0.263514634</v>
       </c>
-      <c r="D21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="D21" t="n">
+        <v>0.32590120071441</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
         <v>0.324550493595855</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>7.76777594040046</v>
       </c>
-      <c r="G21"/>
       <c r="H21"/>
+      <c r="I21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" t="n">
         <v>0.811937246128919</v>
@@ -974,17 +1046,20 @@
       <c r="C22" t="n">
         <v>0.263514634</v>
       </c>
-      <c r="D22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="D22" t="n">
+        <v>0.32590120071441</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
         <v>0.324550493595855</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>11.6535292051355</v>
       </c>
-      <c r="G22"/>
       <c r="H22"/>
+      <c r="I22"/>
     </row>
     <row r="23">
       <c r="A23"/>
@@ -992,15 +1067,18 @@
         <v>0.642296221613004</v>
       </c>
       <c r="C23"/>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23"/>
-      <c r="F23" t="n">
+      <c r="D23" t="n">
+        <v>0.376023859901767</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23"/>
+      <c r="G23" t="n">
         <v>32.6657378105105</v>
       </c>
-      <c r="G23"/>
       <c r="H23"/>
+      <c r="I23"/>
     </row>
     <row r="24">
       <c r="A24"/>
@@ -1008,41 +1086,43 @@
         <v>0.642296221613004</v>
       </c>
       <c r="C24"/>
-      <c r="D24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24"/>
-      <c r="F24" t="n">
+      <c r="D24" t="n">
+        <v>0.376023859901767</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24"/>
+      <c r="G24" t="n">
         <v>51.8803209902535</v>
       </c>
-      <c r="G24"/>
       <c r="H24"/>
+      <c r="I24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.665515738525423</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B25"/>
       <c r="C25" t="n">
-        <v>0.24384</v>
-      </c>
-      <c r="D25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.366392537222747</v>
-      </c>
-      <c r="F25" t="n">
-        <v>8.06121522971138</v>
-      </c>
-      <c r="G25"/>
-      <c r="H25"/>
+        <v>0.325088006</v>
+      </c>
+      <c r="D25"/>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25"/>
+      <c r="G25" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B26" t="n">
         <v>0.665515738525423</v>
@@ -1050,21 +1130,24 @@
       <c r="C26" t="n">
         <v>0.24384</v>
       </c>
-      <c r="D26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" t="n">
+      <c r="D26" t="n">
+        <v>0.369163349974895</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="n">
         <v>0.366392537222747</v>
       </c>
-      <c r="F26" t="n">
-        <v>7.86315235595587</v>
-      </c>
-      <c r="G26"/>
+      <c r="G26" t="n">
+        <v>8.06121522971138</v>
+      </c>
       <c r="H26"/>
+      <c r="I26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B27" t="n">
         <v>0.665515738525423</v>
@@ -1072,47 +1155,49 @@
       <c r="C27" t="n">
         <v>0.24384</v>
       </c>
-      <c r="D27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="D27" t="n">
+        <v>0.369163349974895</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="n">
         <v>0.366392537222747</v>
       </c>
-      <c r="F27" t="n">
-        <v>30.1775506886923</v>
-      </c>
-      <c r="G27"/>
+      <c r="G27" t="n">
+        <v>7.86315235595587</v>
+      </c>
       <c r="H27"/>
+      <c r="I27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B28" t="n">
-        <v>0.668317114820986</v>
+        <v>0.665515738525423</v>
       </c>
       <c r="C28" t="n">
-        <v>0.392848743</v>
-      </c>
-      <c r="D28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.587817870121772</v>
+        <v>0.24384</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.369163349974895</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>23.5311528312165</v>
+        <v>0.366392537222747</v>
       </c>
       <c r="G28" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="H28" t="n">
-        <v>71.94</v>
-      </c>
+        <v>30.1775506886923</v>
+      </c>
+      <c r="H28"/>
+      <c r="I28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B29" t="n">
         <v>0.668317114820986</v>
@@ -1120,51 +1205,57 @@
       <c r="C29" t="n">
         <v>0.392848743</v>
       </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="D29" t="n">
+        <v>0.368335646713147</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="n">
         <v>0.587817870121772</v>
       </c>
-      <c r="F29" t="n">
-        <v>18.7032454447693</v>
-      </c>
       <c r="G29" t="n">
+        <v>23.5311528312165</v>
+      </c>
+      <c r="H29" t="n">
         <v>0.975</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>71.94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B30" t="n">
-        <v>0.655806791819171</v>
+        <v>0.668317114820986</v>
       </c>
       <c r="C30" t="n">
         <v>0.392848743</v>
       </c>
-      <c r="D30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.599031220628655</v>
+      <c r="D30" t="n">
+        <v>0.368335646713147</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>15.9745813671168</v>
+        <v>0.587817870121772</v>
       </c>
       <c r="G30" t="n">
-        <v>1.42</v>
+        <v>18.7032454447693</v>
       </c>
       <c r="H30" t="n">
-        <v>71.9429</v>
+        <v>0.975</v>
+      </c>
+      <c r="I30" t="n">
+        <v>71.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B31" t="n">
         <v>0.655806791819171</v>
@@ -1172,19 +1263,51 @@
       <c r="C31" t="n">
         <v>0.392848743</v>
       </c>
-      <c r="D31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="D31" t="n">
+        <v>0.372031985248788</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
         <v>0.599031220628655</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
+        <v>15.9745813671168</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I31" t="n">
+        <v>71.9429</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.655806791819171</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.392848743</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.372031985248788</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.599031220628655</v>
+      </c>
+      <c r="G32" t="n">
         <v>17.496680423021</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H32" t="n">
         <v>1.42</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I32" t="n">
         <v>71.9429</v>
       </c>
     </row>
@@ -1224,10 +1347,13 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="n">
         <v>0.500234239386116</v>
@@ -1235,25 +1361,28 @@
       <c r="C2" t="n">
         <v>0.13716</v>
       </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" t="n">
+        <v>0.158216629886393</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.274191547080667</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>8.06177138959401</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>6.25</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>72.5453</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
         <v>0.500234239386116</v>
@@ -1261,25 +1390,28 @@
       <c r="C3" t="n">
         <v>0.13716</v>
       </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="D3" t="n">
+        <v>0.158216629886393</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.274191547080667</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>8.00924232633145</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>6.25</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>72.5453</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="n">
         <v>0.500234239386116</v>
@@ -1287,25 +1419,28 @@
       <c r="C4" t="n">
         <v>0.13716</v>
       </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4" t="n">
+        <v>0.158216629886393</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.274191547080667</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>20.7597023796497</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>6.25</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>72.5453</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="n">
         <v>0.49838619196324</v>
@@ -1313,25 +1448,28 @@
       <c r="C5" t="n">
         <v>0.195072</v>
       </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" t="n">
+        <v>0.159179462831171</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.391407312533226</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>11.7604829329048</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>4.8</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>73.18875</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
         <v>0.49838619196324</v>
@@ -1339,25 +1477,28 @@
       <c r="C6" t="n">
         <v>0.195072</v>
       </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6" t="n">
+        <v>0.159179462831171</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.391407312533226</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>11.63069034185</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>4.8</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>73.18875</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
         <v>0.496481994488156</v>
@@ -1365,21 +1506,24 @@
       <c r="C7" t="n">
         <v>0.185928</v>
       </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" t="n">
+        <v>0.160171549960365</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.374490922257273</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>16.0824648775331</v>
       </c>
-      <c r="G7"/>
       <c r="H7"/>
+      <c r="I7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="n">
         <v>0.496481994488156</v>
@@ -1387,21 +1531,24 @@
       <c r="C8" t="n">
         <v>0.185928</v>
       </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8" t="n">
+        <v>0.160171549960365</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="n">
         <v>0.374490922257273</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>19.2785499674532</v>
       </c>
-      <c r="G8"/>
       <c r="H8"/>
+      <c r="I8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="n">
         <v>0.493640731131161</v>
@@ -1409,21 +1556,24 @@
       <c r="C9" t="n">
         <v>0.176784</v>
       </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9" t="n">
+        <v>0.161651848534439</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.358122798325222</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>18.3266040851639</v>
       </c>
-      <c r="G9"/>
       <c r="H9"/>
+      <c r="I9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n">
         <v>0.493640731131161</v>
@@ -1431,21 +1581,24 @@
       <c r="C10" t="n">
         <v>0.176784</v>
       </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10" t="n">
+        <v>0.161651848534439</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.358122798325222</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>18.2382190592684</v>
       </c>
-      <c r="G10"/>
       <c r="H10"/>
+      <c r="I10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n">
         <v>0.493640731131161</v>
@@ -1453,21 +1606,24 @@
       <c r="C11" t="n">
         <v>0.176784</v>
       </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11" t="n">
+        <v>0.161651848534439</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.358122798325222</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>15.8324828082942</v>
       </c>
-      <c r="G11"/>
       <c r="H11"/>
+      <c r="I11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>0.480142518493852</v>
@@ -1475,25 +1631,28 @@
       <c r="C12" t="n">
         <v>0.201168</v>
       </c>
-      <c r="D12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12" t="n">
+        <v>0.168684419052893</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="n">
         <v>0.418975600475957</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>12.5427239203201</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>5.58</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>73.18875</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13" t="n">
         <v>0.480142518493852</v>
@@ -1501,25 +1660,28 @@
       <c r="C13" t="n">
         <v>0.201168</v>
       </c>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="D13" t="n">
+        <v>0.168684419052893</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" t="n">
         <v>0.418975600475957</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>10.1239637211241</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>5.58</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>73.18875</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" t="n">
         <v>0.480142518493852</v>
@@ -1527,25 +1689,28 @@
       <c r="C14" t="n">
         <v>0.201168</v>
       </c>
-      <c r="D14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14" t="n">
+        <v>0.168684419052893</v>
+      </c>
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" t="n">
         <v>0.418975600475957</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>9.98828363272606</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>5.58</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>73.18875</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15" t="n">
         <v>0.487380094779249</v>
@@ -1553,25 +1718,28 @@
       <c r="C15" t="n">
         <v>0.2032</v>
       </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15" t="n">
+        <v>0.164913640878229</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" t="n">
         <v>0.416923058977277</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>15.4910843879708</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>4.685</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>72.485</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B16" t="n">
         <v>0.487380094779249</v>
@@ -1579,25 +1747,28 @@
       <c r="C16" t="n">
         <v>0.2032</v>
       </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="D16" t="n">
+        <v>0.164913640878229</v>
+      </c>
+      <c r="E16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" t="n">
         <v>0.416923058977277</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>15.4221891345314</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>4.685</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>72.485</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="n">
         <v>0.466331392349254</v>
@@ -1605,21 +1776,24 @@
       <c r="C17" t="n">
         <v>0.1016</v>
       </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17" t="n">
+        <v>0.175880017548851</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" t="n">
         <v>0.217870813903748</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>28.8790872259084</v>
       </c>
-      <c r="G17"/>
       <c r="H17"/>
+      <c r="I17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" t="n">
         <v>0.449593987489264</v>
@@ -1627,21 +1801,24 @@
       <c r="C18" t="n">
         <v>0.140208</v>
       </c>
-      <c r="D18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="D18" t="n">
+        <v>0.184600207631533</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.311854704247681</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>31.8776961493743</v>
       </c>
-      <c r="G18"/>
       <c r="H18"/>
+      <c r="I18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" t="n">
         <v>0.42847041975631</v>
@@ -1649,23 +1826,26 @@
       <c r="C19" t="n">
         <v>0.17526</v>
       </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="D19" t="n">
+        <v>0.195605589134617</v>
+      </c>
+      <c r="E19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" t="n">
         <v>0.409036404659342</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>32.3797008299166</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>4.685</v>
       </c>
-      <c r="H19"/>
+      <c r="I19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20" t="n">
         <v>0.42847041975631</v>
@@ -1673,19 +1853,22 @@
       <c r="C20" t="n">
         <v>0.17526</v>
       </c>
-      <c r="D20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="D20" t="n">
+        <v>0.195605589134617</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" t="n">
         <v>0.409036404659342</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>32.2741444383453</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>4.685</v>
       </c>
-      <c r="H20"/>
+      <c r="I20"/>
     </row>
     <row r="21">
       <c r="A21"/>
@@ -1693,15 +1876,18 @@
         <v>0.408678976025888</v>
       </c>
       <c r="C21"/>
-      <c r="D21" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21"/>
-      <c r="F21" t="n">
+      <c r="D21" t="n">
+        <v>0.205916933861214</v>
+      </c>
+      <c r="E21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21" t="n">
         <v>19.5454107221835</v>
       </c>
-      <c r="G21"/>
       <c r="H21"/>
+      <c r="I21"/>
     </row>
     <row r="22">
       <c r="A22"/>
@@ -1709,15 +1895,18 @@
         <v>0.408678976025888</v>
       </c>
       <c r="C22"/>
-      <c r="D22" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22"/>
-      <c r="F22" t="n">
+      <c r="D22" t="n">
+        <v>0.205916933861214</v>
+      </c>
+      <c r="E22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22" t="n">
         <v>19.3542063534147</v>
       </c>
-      <c r="G22"/>
       <c r="H22"/>
+      <c r="I22"/>
     </row>
     <row r="23">
       <c r="A23"/>
@@ -1725,19 +1914,22 @@
         <v>0.41829191635495</v>
       </c>
       <c r="C23"/>
-      <c r="D23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23"/>
-      <c r="F23" t="n">
+      <c r="D23" t="n">
+        <v>0.200908590714584</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23"/>
+      <c r="G23" t="n">
         <v>21.2301041068087</v>
       </c>
-      <c r="G23"/>
       <c r="H23"/>
+      <c r="I23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24" t="n">
         <v>0.57001899623788</v>
@@ -1745,47 +1937,47 @@
       <c r="C24" t="n">
         <v>0.090498812</v>
       </c>
-      <c r="D24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="D24" t="n">
+        <v>0.121858762599824</v>
+      </c>
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" t="n">
         <v>0.158764554510098</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>-0.00277293146331879</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>4.6</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>72.91894</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.550688953475658</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B25"/>
       <c r="C25" t="n">
-        <v>0.132051846</v>
-      </c>
-      <c r="D25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.239793889393565</v>
-      </c>
-      <c r="F25" t="n">
-        <v>44.7430716966125</v>
-      </c>
-      <c r="G25"/>
+        <v>0.074432234</v>
+      </c>
+      <c r="D25"/>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25"/>
+      <c r="G25" t="e">
+        <v>#NUM!</v>
+      </c>
       <c r="H25"/>
+      <c r="I25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B26" t="n">
         <v>0.550688953475658</v>
@@ -1793,61 +1985,95 @@
       <c r="C26" t="n">
         <v>0.132051846</v>
       </c>
-      <c r="D26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" t="n">
+      <c r="D26" t="n">
+        <v>0.131929717362702</v>
+      </c>
+      <c r="E26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" t="n">
         <v>0.239793889393565</v>
       </c>
-      <c r="F26" t="n">
-        <v>44.5809051041735</v>
-      </c>
-      <c r="G26"/>
+      <c r="G26" t="n">
+        <v>44.7430716966125</v>
+      </c>
       <c r="H26"/>
+      <c r="I26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B27" t="n">
-        <v>0.529134093225698</v>
+        <v>0.550688953475658</v>
       </c>
       <c r="C27" t="n">
-        <v>0.16555581</v>
-      </c>
-      <c r="D27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.312880632942666</v>
+        <v>0.132051846</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.131929717362702</v>
+      </c>
+      <c r="E27" t="s">
+        <v>22</v>
       </c>
       <c r="F27" t="n">
-        <v>17.6122685000138</v>
-      </c>
-      <c r="G27"/>
+        <v>0.239793889393565</v>
+      </c>
+      <c r="G27" t="n">
+        <v>44.5809051041735</v>
+      </c>
       <c r="H27"/>
+      <c r="I27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B28" t="n">
+        <v>0.529134093225698</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.16555581</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.143159802322563</v>
+      </c>
+      <c r="E28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.312880632942666</v>
+      </c>
+      <c r="G28" t="n">
+        <v>17.6122685000138</v>
+      </c>
+      <c r="H28"/>
+      <c r="I28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" t="n">
         <v>0.514332621892048</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C29" t="n">
         <v>0.151357905</v>
       </c>
-      <c r="D28" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="D29" t="n">
+        <v>0.15087137078927</v>
+      </c>
+      <c r="E29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" t="n">
         <v>0.294280196428544</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G29" t="n">
         <v>10.1166828097989</v>
       </c>
-      <c r="G28"/>
-      <c r="H28"/>
+      <c r="H29"/>
+      <c r="I29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1885,10 +2111,13 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="n">
         <v>0.846295815451584</v>
@@ -1896,21 +2125,24 @@
       <c r="C2" t="n">
         <v>0.389272031</v>
       </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" t="n">
+        <v>0.329251083203537</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.459971589003172</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>7.8958984290259</v>
       </c>
-      <c r="G2"/>
       <c r="H2"/>
+      <c r="I2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="n">
         <v>0.890397727107957</v>
@@ -1918,21 +2150,24 @@
       <c r="C3" t="n">
         <v>0.24384</v>
       </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="D3" t="n">
+        <v>0.322516373600243</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.273855146499532</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>6.26316980855331</v>
       </c>
-      <c r="G3"/>
       <c r="H3"/>
+      <c r="I3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="n">
         <v>1.27953224172301</v>
@@ -1940,21 +2175,24 @@
       <c r="C4" t="n">
         <v>0.277306992</v>
       </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4" t="n">
+        <v>0.263092465335883</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.216725286755245</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>4.17908012369488</v>
       </c>
-      <c r="G4"/>
       <c r="H4"/>
+      <c r="I4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>1.93587245637372</v>
@@ -1962,21 +2200,24 @@
       <c r="C5" t="n">
         <v>0.152032679</v>
       </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" t="n">
+        <v>0.16286414006333</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.0785344501903744</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>9.28861808820387</v>
       </c>
-      <c r="G5"/>
       <c r="H5"/>
+      <c r="I5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>2.47806654673736</v>
@@ -1984,21 +2225,24 @@
       <c r="C6" t="n">
         <v>0.099617104</v>
       </c>
-      <c r="D6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6" t="n">
+        <v>0.080066827881655</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.0401995273820053</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1.91650182628218</v>
       </c>
-      <c r="G6"/>
       <c r="H6"/>
+      <c r="I6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" t="n">
         <v>1.77503019033284</v>
@@ -2006,21 +2250,24 @@
       <c r="C7" t="n">
         <v>0.209043526</v>
       </c>
-      <c r="D7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" t="n">
+        <v>0.187426022145932</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.117768997473109</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>4.44794425583971</v>
       </c>
-      <c r="G7"/>
       <c r="H7"/>
+      <c r="I7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="n">
         <v>1.70758020779956</v>
@@ -2028,21 +2275,24 @@
       <c r="C8" t="n">
         <v>0.143641857</v>
       </c>
-      <c r="D8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8" t="n">
+        <v>0.197726166245088</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
         <v>0.084120122934138</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>8.19380635018873</v>
       </c>
-      <c r="G8"/>
       <c r="H8"/>
+      <c r="I8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
         <v>1.49225910971257</v>
@@ -2050,21 +2300,24 @@
       <c r="C9" t="n">
         <v>0.217546613</v>
       </c>
-      <c r="D9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9" t="n">
+        <v>0.2306073954847</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.145783404225224</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>11.9818170184072</v>
       </c>
-      <c r="G9"/>
       <c r="H9"/>
+      <c r="I9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" t="n">
         <v>1.49225910971257</v>
@@ -2072,21 +2325,24 @@
       <c r="C10" t="n">
         <v>0.217546613</v>
       </c>
-      <c r="D10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10" t="n">
+        <v>0.2306073954847</v>
+      </c>
+      <c r="E10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.145783404225224</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>11.9908106789727</v>
       </c>
-      <c r="G10"/>
       <c r="H10"/>
+      <c r="I10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" t="n">
         <v>1.11609574558469</v>
@@ -2094,17 +2350,20 @@
       <c r="C11" t="n">
         <v>0.291693421</v>
       </c>
-      <c r="D11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11" t="n">
+        <v>0.288050506806914</v>
+      </c>
+      <c r="E11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.261351610875634</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>8.53166620647352</v>
       </c>
-      <c r="G11"/>
       <c r="H11"/>
+      <c r="I11"/>
     </row>
     <row r="12">
       <c r="A12"/>
@@ -2112,81 +2371,110 @@
         <v>1.00713808149247</v>
       </c>
       <c r="C12"/>
-      <c r="D12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12"/>
-      <c r="F12" t="n">
+      <c r="D12" t="n">
+        <v>0.304689201120935</v>
+      </c>
+      <c r="E12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12"/>
+      <c r="G12" t="n">
         <v>9.30520487333494</v>
       </c>
-      <c r="G12"/>
       <c r="H12"/>
+      <c r="I12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.99935539120017</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.245749827</v>
-      </c>
-      <c r="D13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.245908341680999</v>
-      </c>
-      <c r="F13" t="n">
-        <v>16.0453723843845</v>
-      </c>
-      <c r="G13"/>
+        <v>18</v>
+      </c>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13"/>
+      <c r="G13" t="e">
+        <v>#NUM!</v>
+      </c>
       <c r="H13"/>
+      <c r="I13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>0.944876559154064</v>
+        <v>0.99935539120017</v>
       </c>
       <c r="C14" t="n">
-        <v>0.315758887</v>
-      </c>
-      <c r="D14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.334180040705735</v>
+        <v>0.245749827</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.305877679286223</v>
+      </c>
+      <c r="E14" t="s">
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>7.06385924306657</v>
-      </c>
-      <c r="G14"/>
+        <v>0.245908341680999</v>
+      </c>
+      <c r="G14" t="n">
+        <v>16.0453723843845</v>
+      </c>
       <c r="H14"/>
+      <c r="I14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" t="n">
+        <v>0.944876559154064</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.315758887</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.314197026443233</v>
+      </c>
+      <c r="E15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.334180040705735</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7.06385924306657</v>
+      </c>
+      <c r="H15"/>
+      <c r="I15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="n">
         <v>0.874832346523355</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C16" t="n">
         <v>0.270921438</v>
       </c>
-      <c r="D15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D16" t="n">
+        <v>0.324893329930818</v>
+      </c>
+      <c r="E16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" t="n">
         <v>0.30968383722511</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G16" t="n">
         <v>8.2264856374068</v>
       </c>
-      <c r="G15"/>
-      <c r="H15"/>
+      <c r="H16"/>
+      <c r="I16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2224,10 +2512,13 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="n">
         <v>0.275826809729631</v>
@@ -2235,25 +2526,28 @@
       <c r="C2" t="n">
         <v>0.09906</v>
       </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" t="n">
+        <v>0.108072813469553</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.359138403178066</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>24.690084932128</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1.76</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>74.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B3" t="n">
         <v>0.275826809729631</v>
@@ -2261,25 +2555,28 @@
       <c r="C3" t="n">
         <v>0.09906</v>
       </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="D3" t="n">
+        <v>0.108072813469553</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.359138403178066</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>23.1483821264679</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1.76</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>74.42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="n">
         <v>0.14842325926963</v>
@@ -2287,25 +2584,28 @@
       <c r="C4" t="n">
         <v>0.103632</v>
       </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4" t="n">
+        <v>0.11932456079093</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.69821940651323</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>118.259222088889</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1.83</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>73.29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="n">
         <v>0.139418054063201</v>
@@ -2313,21 +2613,24 @@
       <c r="C5" t="n">
         <v>0.100003886</v>
       </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" t="n">
+        <v>0.12011986275225</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.71729509260448</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>50.9547523254218</v>
       </c>
-      <c r="G5"/>
       <c r="H5"/>
+      <c r="I5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="n">
         <v>0.35708644464822</v>
@@ -2335,21 +2638,24 @@
       <c r="C6" t="n">
         <v>0.068341644</v>
       </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6" t="n">
+        <v>0.100896303268462</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.191386833704444</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>9.73092604234097</v>
       </c>
-      <c r="G6"/>
       <c r="H6"/>
+      <c r="I6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" t="n">
         <v>0.35708644464822</v>
@@ -2357,21 +2663,24 @@
       <c r="C7" t="n">
         <v>0.068341644</v>
       </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" t="n">
+        <v>0.100896303268462</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.191386833704444</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>9.55546231205082</v>
       </c>
-      <c r="G7"/>
       <c r="H7"/>
+      <c r="I7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" t="n">
         <v>0.979089072339963</v>
@@ -2379,21 +2688,24 @@
       <c r="C8" t="n">
         <v>0.077164557</v>
       </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8" t="n">
+        <v>0.0459636395024098</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="n">
         <v>0.0788126016109867</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>12.1601192837523</v>
       </c>
-      <c r="G8"/>
       <c r="H8"/>
+      <c r="I8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B9" t="n">
         <v>0.739129107152845</v>
@@ -2401,25 +2713,28 @@
       <c r="C9" t="n">
         <v>0.059129281</v>
       </c>
-      <c r="D9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9" t="n">
+        <v>0.067155897377356</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.0799985826938522</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>7.9516472320781</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1.93</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>74.42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B10" t="n">
         <v>0.506557584543146</v>
@@ -2427,25 +2742,28 @@
       <c r="C10" t="n">
         <v>0.125763952</v>
       </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10" t="n">
+        <v>0.0876956389866292</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.248271777656678</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>30.7702058957052</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>1.53</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>71.74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B11" t="n">
         <v>0.264227453541008</v>
@@ -2453,25 +2771,28 @@
       <c r="C11" t="n">
         <v>0.090472022</v>
       </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11" t="n">
+        <v>0.109097219967282</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.342402050913149</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>34.9833835244488</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1.704</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>73.278</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" t="n">
         <v>0.20547930573848</v>
@@ -2479,23 +2800,26 @@
       <c r="C12" t="n">
         <v>0.10404495</v>
       </c>
-      <c r="D12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12" t="n">
+        <v>0.114285610026165</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" t="n">
         <v>0.506352450559771</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>53.152789367812</v>
       </c>
-      <c r="G12"/>
-      <c r="H12" t="n">
+      <c r="H12"/>
+      <c r="I12" t="n">
         <v>72.6692562</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B13" t="n">
         <v>0.168078940883987</v>
@@ -2503,21 +2827,24 @@
       <c r="C13" t="n">
         <v>0.054061724</v>
       </c>
-      <c r="D13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="D13" t="n">
+        <v>0.117588653415071</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" t="n">
         <v>0.321644839714424</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>33.3410433436497</v>
       </c>
-      <c r="G13"/>
       <c r="H13"/>
+      <c r="I13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" t="n">
         <v>0.257762439351586</v>
@@ -2525,19 +2852,22 @@
       <c r="C14" t="n">
         <v>0.142205108</v>
       </c>
-      <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14" t="n">
+        <v>0.109668182910041</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" t="n">
         <v>0.551690573528572</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>31.9180285667398</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>1.628292683</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>73.679375</v>
       </c>
     </row>
@@ -2547,19 +2877,22 @@
         <v>0.307189767462987</v>
       </c>
       <c r="C15"/>
-      <c r="D15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15"/>
-      <c r="F15" t="n">
+      <c r="D15" t="n">
+        <v>0.105302968560265</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15"/>
+      <c r="G15" t="n">
         <v>15.8650769934215</v>
       </c>
-      <c r="G15"/>
       <c r="H15"/>
+      <c r="I15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" t="n">
         <v>0.24912069961522</v>
@@ -2567,25 +2900,28 @@
       <c r="C16" t="n">
         <v>0.119117488</v>
       </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="D16" t="n">
+        <v>0.110431385125203</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" t="n">
         <v>0.478151707923039</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>26.1959995510725</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>1.78</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>73.43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" t="n">
         <v>0.237998837806854</v>
@@ -2593,21 +2929,24 @@
       <c r="C17" t="n">
         <v>0.230909091</v>
       </c>
-      <c r="D17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17" t="n">
+        <v>0.111413621321598</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" t="n">
         <v>0.970211002405788</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>94.2187481505369</v>
       </c>
-      <c r="G17"/>
       <c r="H17"/>
+      <c r="I17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18" t="n">
         <v>0.267523084070634</v>
@@ -2615,21 +2954,24 @@
       <c r="C18" t="n">
         <v>0.2333</v>
       </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="D18" t="n">
+        <v>0.108806163698834</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.872074276545053</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>115.910838296351</v>
       </c>
-      <c r="G18"/>
       <c r="H18"/>
+      <c r="I18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" t="n">
         <v>0.160568324089945</v>
@@ -2637,17 +2979,20 @@
       <c r="C19" t="n">
         <v>0.2333</v>
       </c>
-      <c r="D19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="D19" t="n">
+        <v>0.118251959595229</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" t="n">
         <v>1.45296403460818</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>42.6142452396609</v>
       </c>
-      <c r="G19"/>
       <c r="H19"/>
+      <c r="I19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2685,32 +3030,32 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.744112571034481</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B2"/>
       <c r="C2" t="n">
-        <v>0.116835492</v>
-      </c>
-      <c r="D2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.157013194707318</v>
-      </c>
-      <c r="F2" t="n">
-        <v>12.0270837749951</v>
-      </c>
-      <c r="G2"/>
+        <v>0.06096</v>
+      </c>
+      <c r="D2"/>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2"/>
+      <c r="G2" t="e">
+        <v>#NUM!</v>
+      </c>
       <c r="H2"/>
+      <c r="I2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" t="n">
         <v>0.744112571034481</v>
@@ -2718,21 +3063,24 @@
       <c r="C3" t="n">
         <v>0.116835492</v>
       </c>
-      <c r="D3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="D3" t="n">
+        <v>0.0876947459669113</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.157013194707318</v>
       </c>
-      <c r="F3" t="n">
-        <v>11.6739000306237</v>
-      </c>
-      <c r="G3"/>
+      <c r="G3" t="n">
+        <v>12.0270837749951</v>
+      </c>
       <c r="H3"/>
+      <c r="I3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="n">
         <v>0.744112571034481</v>
@@ -2740,43 +3088,49 @@
       <c r="C4" t="n">
         <v>0.116835492</v>
       </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4" t="n">
+        <v>0.0876947459669113</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.157013194707318</v>
       </c>
-      <c r="F4" t="n">
-        <v>4.82250048309325</v>
-      </c>
-      <c r="G4"/>
+      <c r="G4" t="n">
+        <v>11.6739000306237</v>
+      </c>
       <c r="H4"/>
+      <c r="I4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" t="n">
-        <v>0.87528110109794</v>
+        <v>0.744112571034481</v>
       </c>
       <c r="C5" t="n">
-        <v>0.089573878</v>
-      </c>
-      <c r="D5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.10233726957847</v>
+        <v>0.116835492</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0876947459669113</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>2.09011876832932</v>
-      </c>
-      <c r="G5"/>
+        <v>0.157013194707318</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.82250048309325</v>
+      </c>
       <c r="H5"/>
+      <c r="I5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="n">
         <v>0.87528110109794</v>
@@ -2784,21 +3138,24 @@
       <c r="C6" t="n">
         <v>0.089573878</v>
       </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6" t="n">
+        <v>0.0761268628377038</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.10233726957847</v>
       </c>
-      <c r="F6" t="n">
-        <v>2.0802072636449</v>
-      </c>
-      <c r="G6"/>
+      <c r="G6" t="n">
+        <v>2.09011876832932</v>
+      </c>
       <c r="H6"/>
+      <c r="I6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" t="n">
         <v>0.87528110109794</v>
@@ -2806,43 +3163,49 @@
       <c r="C7" t="n">
         <v>0.089573878</v>
       </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" t="n">
+        <v>0.0761268628377038</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.10233726957847</v>
       </c>
-      <c r="F7" t="n">
-        <v>3.43485459448428</v>
-      </c>
-      <c r="G7"/>
+      <c r="G7" t="n">
+        <v>2.0802072636449</v>
+      </c>
       <c r="H7"/>
+      <c r="I7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" t="n">
-        <v>1.62598028208757</v>
+        <v>0.87528110109794</v>
       </c>
       <c r="C8" t="n">
-        <v>0.040360478</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.0248222431997649</v>
+        <v>0.089573878</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0761268628377038</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
       </c>
       <c r="F8" t="n">
-        <v>11.4435970636991</v>
-      </c>
-      <c r="G8"/>
+        <v>0.10233726957847</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.43485459448428</v>
+      </c>
       <c r="H8"/>
+      <c r="I8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" t="n">
         <v>1.62598028208757</v>
@@ -2850,43 +3213,49 @@
       <c r="C9" t="n">
         <v>0.040360478</v>
       </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9" t="n">
+        <v>0.0099219554054219</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.0248222431997649</v>
       </c>
-      <c r="F9" t="n">
-        <v>5.24292831173142</v>
-      </c>
-      <c r="G9"/>
+      <c r="G9" t="n">
+        <v>11.4435970636991</v>
+      </c>
       <c r="H9"/>
+      <c r="I9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="n">
-        <v>1.32277923770115</v>
+        <v>1.62598028208757</v>
       </c>
       <c r="C10" t="n">
-        <v>0.032272941</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.024397828511496</v>
+        <v>0.040360478</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0099219554054219</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>8.15035839237917</v>
-      </c>
-      <c r="G10"/>
+        <v>0.0248222431997649</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.24292831173142</v>
+      </c>
       <c r="H10"/>
+      <c r="I10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" t="n">
         <v>1.32277923770115</v>
@@ -2894,169 +3263,187 @@
       <c r="C11" t="n">
         <v>0.032272941</v>
       </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11" t="n">
+        <v>0.0366615570798397</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.024397828511496</v>
       </c>
-      <c r="F11" t="n">
-        <v>22.0957123104932</v>
-      </c>
-      <c r="G11"/>
+      <c r="G11" t="n">
+        <v>8.15035839237917</v>
+      </c>
       <c r="H11"/>
+      <c r="I11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" t="n">
-        <v>1.05356686240279</v>
+        <v>1.32277923770115</v>
       </c>
       <c r="C12" t="n">
-        <v>0.054257143</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.0514985284144757</v>
+        <v>0.032272941</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0366615570798397</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>5.82511509476107</v>
-      </c>
-      <c r="G12"/>
+        <v>0.024397828511496</v>
+      </c>
+      <c r="G12" t="n">
+        <v>22.0957123104932</v>
+      </c>
       <c r="H12"/>
+      <c r="I12"/>
     </row>
     <row r="13">
-      <c r="A13"/>
-      <c r="B13" t="n">
-        <v>0.788949229451763</v>
-      </c>
-      <c r="C13"/>
-      <c r="D13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13"/>
-      <c r="F13" t="n">
-        <v>6.43812602285802</v>
-      </c>
-      <c r="G13"/>
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13"/>
+      <c r="C13" t="n">
+        <v>0.044325555</v>
+      </c>
+      <c r="D13"/>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13"/>
+      <c r="G13" t="e">
+        <v>#NUM!</v>
+      </c>
       <c r="H13"/>
+      <c r="I13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
         <v>34</v>
       </c>
       <c r="B14" t="n">
-        <v>0.737595633206477</v>
+        <v>1.05356686240279</v>
       </c>
       <c r="C14" t="n">
-        <v>0.137964795</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.187046653733888</v>
+        <v>0.054257143</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0604036642215534</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
       </c>
       <c r="F14" t="n">
-        <v>5.56621257188235</v>
-      </c>
-      <c r="G14"/>
+        <v>0.0514985284144757</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.82511509476107</v>
+      </c>
       <c r="H14"/>
+      <c r="I14"/>
     </row>
     <row r="15">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
+      <c r="A15"/>
       <c r="B15" t="n">
-        <v>0.73062868871752</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.14825882</v>
-      </c>
-      <c r="D15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.202919516150181</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5.19498488950373</v>
-      </c>
-      <c r="G15"/>
+        <v>0.788949229451763</v>
+      </c>
+      <c r="C15"/>
+      <c r="D15" t="n">
+        <v>0.0837405564656309</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15"/>
+      <c r="G15" t="n">
+        <v>6.43812602285802</v>
+      </c>
       <c r="H15"/>
+      <c r="I15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" t="n">
-        <v>0.73062868871752</v>
+        <v>0.737595633206477</v>
       </c>
       <c r="C16" t="n">
-        <v>0.14825882</v>
-      </c>
-      <c r="D16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.202919516150181</v>
+        <v>0.137964795</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.0882694811958429</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>5.12626815816108</v>
-      </c>
-      <c r="G16"/>
+        <v>0.187046653733888</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.56621257188235</v>
+      </c>
       <c r="H16"/>
+      <c r="I16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
         <v>37</v>
       </c>
       <c r="B17" t="n">
-        <v>0.742335964836517</v>
+        <v>0.73062868871752</v>
       </c>
       <c r="C17" t="n">
-        <v>0.012192</v>
-      </c>
-      <c r="D17" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.0164238304184616</v>
+        <v>0.14825882</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.08888390295979</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
       </c>
       <c r="F17" t="n">
-        <v>-163.072100172185</v>
-      </c>
-      <c r="G17"/>
+        <v>0.202919516150181</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.19498488950373</v>
+      </c>
       <c r="H17"/>
+      <c r="I17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
         <v>37</v>
       </c>
       <c r="B18" t="n">
-        <v>0.742335964836517</v>
+        <v>0.73062868871752</v>
       </c>
       <c r="C18" t="n">
-        <v>0.012192</v>
-      </c>
-      <c r="D18" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.0164238304184616</v>
+        <v>0.14825882</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.08888390295979</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>-157.057145657638</v>
-      </c>
-      <c r="G18"/>
+        <v>0.202919516150181</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.12626815816108</v>
+      </c>
       <c r="H18"/>
+      <c r="I18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" t="n">
         <v>0.742335964836517</v>
@@ -3064,17 +3451,127 @@
       <c r="C19" t="n">
         <v>0.012192</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" t="n">
+        <v>0.0878514266345586</v>
+      </c>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0164238304184616</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-163.072100172185</v>
+      </c>
+      <c r="H19"/>
+      <c r="I19"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.742335964836517</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.012192</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.0878514266345586</v>
+      </c>
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.0164238304184616</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-157.057145657638</v>
+      </c>
+      <c r="H20"/>
+      <c r="I20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.742335964836517</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.012192</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0878514266345586</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0164238304184616</v>
+      </c>
+      <c r="G21" t="n">
+        <v>53.4876810991007</v>
+      </c>
+      <c r="H21"/>
+      <c r="I21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22"/>
+      <c r="C22" t="n">
+        <v>0.104457388</v>
+      </c>
+      <c r="D22"/>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H22"/>
+      <c r="I22"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
         <v>41</v>
       </c>
-      <c r="E19" t="n">
-        <v>0.0164238304184616</v>
-      </c>
-      <c r="F19" t="n">
-        <v>53.4876810991007</v>
-      </c>
-      <c r="G19"/>
-      <c r="H19"/>
+      <c r="B23"/>
+      <c r="C23" t="n">
+        <v>0.119632672</v>
+      </c>
+      <c r="D23"/>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23"/>
+      <c r="G23" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H23"/>
+      <c r="I23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24"/>
+      <c r="C24" t="n">
+        <v>0.125639851</v>
+      </c>
+      <c r="D24"/>
+      <c r="E24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24"/>
+      <c r="G24" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H24"/>
+      <c r="I24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/04_Outputs/rC_k600.xlsx
+++ b/04_Outputs/rC_k600.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\04_Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samanthahowley\Desktop\SpringMetabolism_FlowReversals\04_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F499DA49-B47A-4DA4-BB8F-F63FA6CDDF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E64B721-29C4-4F01-8ABC-28F8353ED5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AM" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,25 @@
     <sheet name="LF" sheetId="4" r:id="rId4"/>
     <sheet name="OS" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -70,14 +83,14 @@
   <si>
     <t>OS</t>
   </si>
+  <si>
+    <t>I</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -114,7 +127,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -218,181 +231,200 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="power"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="9.6415135608048999E-3"/>
-                  <c:y val="-0.39411708953047536"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>AM!$G$2:$G$23</c:f>
+              <c:f>AM!$G$2:$G$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>0.26929954724057997</c:v>
+                  <c:v>0.239640902998462</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.26591872251684501</c:v>
+                  <c:v>0.24483675340362801</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.26938268888003197</c:v>
+                  <c:v>0.24483675340362801</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.26938268888003197</c:v>
+                  <c:v>0.256226733839999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.25936577783929399</c:v>
+                  <c:v>0.256226733839999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.25936577783929399</c:v>
+                  <c:v>0.25705820430833598</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.24779631643734701</c:v>
+                  <c:v>0.25705820430833598</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.24779631643734701</c:v>
+                  <c:v>0.25846925292986</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.25846925292986</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.6052859302193001</c:v>
+                  <c:v>0.26494909806747902</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.6052859302193001</c:v>
+                  <c:v>0.26494909806747902</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.73846124410021996</c:v>
+                  <c:v>0.26502797555140301</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.73846124410021996</c:v>
+                  <c:v>0.26658216225721099</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.73639287530589403</c:v>
+                  <c:v>0.32557883548586403</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.352445767303255</c:v>
+                  <c:v>0.32700939804183699</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.34979625322111801</c:v>
+                  <c:v>0.35825069383838998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.34624235777991702</c:v>
+                  <c:v>0.35891220134342799</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.236309150486498</c:v>
+                  <c:v>0.36459096455608803</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.41818901391054503</c:v>
+                  <c:v>0.36459096455608803</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.41485994116438002</c:v>
+                  <c:v>0.36465776923577697</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.245623597499528</c:v>
+                  <c:v>0.41010863057300501</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.245623597499528</c:v>
+                  <c:v>0.41065339316936</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.73861822689876599</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.73935259974152701</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.73935259974152701</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.88614433356157496</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.88614433356157496</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.88741132439375403</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.94276859487791098</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.94276859487791098</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.60103975950207</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.60103975950207</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>AM!$H$2:$H$23</c:f>
+              <c:f>AM!$H$2:$H$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>21.369670657725798</c:v>
+                </c:pt>
                 <c:pt idx="3">
-                  <c:v>37.438864801751997</c:v>
+                  <c:v>6.0246525978349297</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.707887873600399</c:v>
+                  <c:v>13.892989272610601</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20.5111754182536</c:v>
+                  <c:v>20.528070790228</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>21.29534890235</c:v>
+                  <c:v>22.590230949448301</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>23.4345864630479</c:v>
+                  <c:v>20.779715129995601</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20.582320358999102</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.9111329260555596</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.4632456631712998</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2.1537714224900602</c:v>
+                  <c:v>10.1577577965675</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.1639379833854999</c:v>
+                  <c:v>25.708252717455</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.0894276044164304</c:v>
+                  <c:v>25.6620546637158</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>23.990345725040498</c:v>
+                  <c:v>6.9745538382867203</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>24.1740006502773</c:v>
+                  <c:v>6.9616991075446499</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>21.6709643391052</c:v>
+                  <c:v>16.279117207498601</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.7191684375126197</c:v>
+                  <c:v>21.051811488658899</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>10.6037922821831</c:v>
+                  <c:v>16.544827851223001</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>42.991528895930301</c:v>
+                  <c:v>10.726642441441401</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>68.335187975973895</c:v>
+                  <c:v>6.8424673213972902</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.1574183462267702</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.4566592322269702</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.1511748585391199</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.8211227677034598</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.1187175452266498</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.1044984311737398</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.3105955732377901</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.36490590126142</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.45773182901047699</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.58021307026655</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -400,7 +432,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-356A-4805-A904-75D96C4B06BC}"/>
+              <c16:uniqueId val="{00000000-8685-4F4E-942B-4C94A9623687}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -412,11 +444,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1640856271"/>
-        <c:axId val="1640856751"/>
+        <c:axId val="331664303"/>
+        <c:axId val="331664783"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1640856271"/>
+        <c:axId val="331664303"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -473,12 +505,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1640856751"/>
+        <c:crossAx val="331664783"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1640856751"/>
+        <c:axId val="331664783"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -535,7 +567,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1640856271"/>
+        <c:crossAx val="331664303"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -677,208 +709,152 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.153078851963413"/>
-                  <c:y val="-0.41238223813701608"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>GB!$F$2:$F$27</c:f>
+              <c:f>GB!$G$2:$G$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>6772.2275483438798</c:v>
+                  <c:v>0.39570458731269098</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6522.0305392485297</c:v>
+                  <c:v>0.395724677442572</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5983.8444990745702</c:v>
+                  <c:v>0.41314429687603998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5916.7378643532802</c:v>
+                  <c:v>0.41420772624117003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6562.7722472662899</c:v>
+                  <c:v>0.41427437299901998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>573.20000000000005</c:v>
+                  <c:v>0.437729121568594</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6107.8958463442596</c:v>
+                  <c:v>0.47310841336748199</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6017.3477409245197</c:v>
+                  <c:v>0.473199183951164</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5588.1246494146499</c:v>
+                  <c:v>0.473199183951164</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5588.1246494146499</c:v>
+                  <c:v>0.486286253704515</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5774.7404078712798</c:v>
+                  <c:v>0.48686892584765001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5774.7404078712798</c:v>
+                  <c:v>0.492752758154543</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5772.5353821522203</c:v>
+                  <c:v>0.492752758154543</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5684.7840110370498</c:v>
+                  <c:v>0.497716180087658</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5684.7840110370498</c:v>
+                  <c:v>0.49773357358562098</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>6021.9090408438997</c:v>
+                  <c:v>0.49773357358562098</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6021.9090408438997</c:v>
+                  <c:v>0.49782071547936002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5837.03059602348</c:v>
+                  <c:v>0.49782071547936002</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5604.25032645599</c:v>
+                  <c:v>0.512233193314514</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5530.1392519331903</c:v>
+                  <c:v>0.52959181897001695</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5600.2851635686502</c:v>
+                  <c:v>0.53593698976396698</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5679.94985068187</c:v>
+                  <c:v>0.55030838061051701</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5622.7792873607596</c:v>
+                  <c:v>0.550502530962522</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5640.0318337175104</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>5433.1613828108102</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>5473.2343954034995</c:v>
+                  <c:v>0.56969572112081401</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>GB!$H$2:$H$27</c:f>
+              <c:f>GB!$H$2:$H$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>10.088633653432099</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9894337092864802</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.818929035817799</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.7661132110034</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16.818242674381999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16.428025299675401</c:v>
+                </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.0402645513699502</c:v>
+                  <c:v>9.6476919720071006</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.9921305911887899</c:v>
+                  <c:v>9.5993216311403806</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.9088682106652497</c:v>
+                  <c:v>8.3328428116839692</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.8149297981260997</c:v>
+                  <c:v>7.8022981892533503</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.2302959995820704</c:v>
+                  <c:v>7.7583020845305404</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9.7963568543513109</c:v>
+                  <c:v>8.2068053410079695</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.39767988696053</c:v>
+                  <c:v>9.7683963928870696</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9.2913026472153</c:v>
+                  <c:v>4.03684971713494</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8.0654620659721097</c:v>
+                  <c:v>4.0104061748601199</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>6.4953401493818799</c:v>
+                  <c:v>10.530608571701499</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.2541923592863702</c:v>
+                  <c:v>5.9426733122948399</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.1905251222689399</c:v>
+                  <c:v>5.8481974706796702</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>7.7574062421653602</c:v>
+                  <c:v>3.5060297572933301</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7.8334799626330902</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>15.995905428480199</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>16.2023095487049</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>16.4363904026123</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>9.7293311774023596</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>9.7076598625162198</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>10.353699747649699</c:v>
+                  <c:v>8.8934299493761699</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -886,7 +862,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-803D-4124-B6E3-AE3C5EA71914}"/>
+              <c16:uniqueId val="{00000000-7E2C-46E7-B2F9-7847A9DDA159}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -898,11 +874,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1640769391"/>
-        <c:axId val="1640771311"/>
+        <c:axId val="331669103"/>
+        <c:axId val="331673903"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1640769391"/>
+        <c:axId val="331669103"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -959,12 +935,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1640771311"/>
+        <c:crossAx val="331673903"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1640771311"/>
+        <c:axId val="331673903"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1021,7 +997,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1640769391"/>
+        <c:crossAx val="331669103"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1163,56 +1139,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="power"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.10801640419947507"/>
-                  <c:y val="-0.66551399825021873"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>ID!$G$2:$G$16</c:f>
@@ -1220,49 +1146,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>0.88949597204892406</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.89694420076360204</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.89966739347265001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.90011033030870202</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.94090301323553105</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97722836908240696</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.99589610999220601</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.97722836908240696</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.94090301323553105</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.89966739347265001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.88949597204892406</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.90011033030870202</c:v>
-                </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
+                  <c:v>1.0442543706910099</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>1.2366864918379299</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
+                  <c:v>1.4229669796427999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.4304669796428</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.6347916457732701</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.71905533629398</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>1.85747687368365</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="14">
                   <c:v>2.4218717197483</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.71905533629398</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.6347916457732701</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.43046697964281</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.4229669796428099</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.0442543706910099</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.89694420076360104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1274,37 +1200,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>3.1998276591435801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.2067473398202804</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.6055235509349699</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.1209961501293702</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.2336938360616001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.4659573982030203</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>3.6359854222587802</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.4659573982030203</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.2336938360616001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.6055235509349699</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.1998276591435801</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3.1209961501293702</c:v>
-                </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
+                  <c:v>4.6176963145351104</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2.1878451594958102</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
+                  <c:v>6.3531601948909397</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.3151101233337998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.8892751359493398</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.3123306997931201</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.1959327736538397</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>1.01033184827849</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2.3123306997931201</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>4.6176963145351202</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5.2067473398202901</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1312,7 +1250,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FEB7-4036-A9FE-731250A025E8}"/>
+              <c16:uniqueId val="{00000000-A464-464A-810A-16409ECE4744}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1324,11 +1262,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1640768911"/>
-        <c:axId val="1640770351"/>
+        <c:axId val="331663343"/>
+        <c:axId val="2008459903"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1640768911"/>
+        <c:axId val="331663343"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1385,12 +1323,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1640770351"/>
+        <c:crossAx val="2008459903"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1640770351"/>
+        <c:axId val="2008459903"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1447,7 +1385,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1640768911"/>
+        <c:crossAx val="331663343"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1589,56 +1527,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="power"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="5.5630796150481193E-2"/>
-                  <c:y val="-0.3650991542723826"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>LF!$G$2:$G$19</c:f>
@@ -1646,58 +1534,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>0.41324602598597798</c:v>
+                  <c:v>0.232705782824495</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.30467043072306799</c:v>
+                  <c:v>0.26724465813797499</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.445617932445036</c:v>
+                  <c:v>0.283060203628272</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.36046910737976201</c:v>
+                  <c:v>0.28406916777292901</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.287405278189796</c:v>
+                  <c:v>0.29357637887200599</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.25664809803313798</c:v>
+                  <c:v>0.30356611946985401</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.284917010811369</c:v>
+                  <c:v>0.30794118768866002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.43639688737785798</c:v>
+                  <c:v>0.31663227546399703</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.49579255476263101</c:v>
+                  <c:v>0.31948997437322302</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.480629804545051</c:v>
+                  <c:v>0.32111502024014399</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0466739120111399</c:v>
+                  <c:v>0.32813007464273403</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.79710907302071798</c:v>
+                  <c:v>0.342845759934436</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.61655902950461705</c:v>
+                  <c:v>0.40915209872903202</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.441514938764208</c:v>
+                  <c:v>0.44151648579325398</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.34602005466925301</c:v>
+                  <c:v>0.44370136881571698</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.27803049853348299</c:v>
+                  <c:v>0.59685227693446097</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.21894230032698</c:v>
+                  <c:v>0.77273115566626005</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.232917931310444</c:v>
+                  <c:v>1.0455348823919599</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1708,53 +1596,50 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>4.7857105061486997</c:v>
-                </c:pt>
                 <c:pt idx="1">
-                  <c:v>22.843809113422701</c:v>
+                  <c:v>6.6366929502241296</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.9203127323219196</c:v>
+                  <c:v>10.1472603647596</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.1107619693398103</c:v>
+                  <c:v>5.2612293332181004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.9106353655349597</c:v>
+                  <c:v>7.56519155189988</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>23.182547856377401</c:v>
+                  <c:v>10.0391794953904</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.0896583277326002</c:v>
+                  <c:v>6.2459704882807001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.70052389288857</c:v>
+                  <c:v>6.3966655790962204</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.75156963455646</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.6852047257509399</c:v>
+                  <c:v>6.32249939376835</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.7689956626427303</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.0380784985144702</c:v>
+                  <c:v>6.0301251612138902</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.5881197864225403</c:v>
+                  <c:v>1.9095710181134999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8.9343863614644494</c:v>
+                  <c:v>1.8973495018753599</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8.2600141156089606</c:v>
+                  <c:v>4.17140699017712</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>13.1656779100593</c:v>
+                  <c:v>1.7383691170511399</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>6.6314029468288096</c:v>
+                  <c:v>1.78592995957968</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1762,7 +1647,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-549A-4122-A9D7-000C853DA1D0}"/>
+              <c16:uniqueId val="{00000000-2AF3-45B5-A580-81AAFA0B8459}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1774,11 +1659,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1640862991"/>
-        <c:axId val="1640861551"/>
+        <c:axId val="443713087"/>
+        <c:axId val="443727487"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1640862991"/>
+        <c:axId val="443713087"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1835,12 +1720,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1640861551"/>
+        <c:crossAx val="443727487"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1640861551"/>
+        <c:axId val="443727487"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1897,7 +1782,437 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1640862991"/>
+        <c:crossAx val="443713087"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>OS!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>k600_1.day</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>OS!$G$2:$G$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0.73060288362784198</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.73067292779711301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.73279435804070603</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.73980051064202401</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.73988407796505096</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.73988407796505096</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.74079475097583203</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.74079475097583203</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.74090071769494803</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.74132115970993895</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.74252870479035604</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.74252870479035604</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.74281434911411404</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.82876864696313601</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.89351335106295304</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.89625197176154203</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.89625197176154203</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.0582857713989</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.29844388483991</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.29844388483991</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.63794044253354</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.63944889300297</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>OS!$H$2:$H$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>1.59154333122255</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.58923907068933</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.7368096314749899</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.8778279962626208</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.8829655753754899</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.4676512805746391</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.54684612115962805</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.59890717896635304</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.54649356478142497</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.1536506647998497</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.5709301178400801</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.1664842881561501</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.1882598556347701</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.92360478234698296</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.920782581387938</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.52308029952103</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.6141643911102601</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.9396406411534199</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.87039388474377</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.0845577324962603</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.3965278925312901</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-995E-4D0E-B289-2F2943AB0CAB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="443726527"/>
+        <c:axId val="443720287"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="443726527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="443720287"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="443720287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="443726527"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2113,6 +2428,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -4177,27 +4532,543 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>280987</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>280987</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CFA3DD3-B834-EB01-83D7-48F579C6AF0E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B24B5912-EEED-10DC-B610-D16312187B2B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4223,22 +5094,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>33337</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>100012</xdr:rowOff>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13A02E1C-3465-2621-B0A5-A8E21B8FE5CE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16466CD1-F9B3-5BB6-0395-C61521B25392}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4263,15 +5134,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>404812</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>147637</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>404812</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>33337</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4279,7 +5150,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{433711D2-662F-ACD1-5203-F5C62EBA620D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{745E5555-39B8-D127-FF59-AD6B67962F6D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4304,23 +5175,64 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDF5A939-C399-6109-081F-6543B195DDE5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED06A681-82BE-DDD5-2ECD-E17323E28716}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EB5406E-DCBA-F89D-736A-52C0FB272E73}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4620,7 +5532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4654,7 +5566,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>44872</v>
+        <v>45064</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -4662,22 +5574,28 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="e">
-        <v>#NUM!</v>
+      <c r="D2">
+        <v>21.72</v>
       </c>
       <c r="E2">
-        <v>1798.8</v>
+        <v>24084</v>
       </c>
       <c r="F2">
-        <v>1182.0619999999999</v>
+        <v>4387.2</v>
       </c>
       <c r="G2">
-        <v>0.26929954724057997</v>
+        <v>0.239640902998462</v>
+      </c>
+      <c r="H2">
+        <v>21.369670657725798</v>
+      </c>
+      <c r="I2">
+        <v>0.21888147684550499</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>44886</v>
+        <v>45086</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -4686,132 +5604,132 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <v>21.43</v>
+        <v>22.22</v>
       </c>
       <c r="E3">
-        <v>21006</v>
+        <v>22506</v>
       </c>
       <c r="F3">
-        <v>4236.6000000000004</v>
+        <v>4932</v>
       </c>
       <c r="G3">
-        <v>0.26591872251684501</v>
+        <v>0.24483675340362801</v>
       </c>
       <c r="I3">
-        <v>0.114052710685128</v>
+        <v>0.458224391330884</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>44886</v>
+        <v>45086</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>21.43</v>
+        <v>22.22</v>
       </c>
       <c r="E4">
-        <v>20514</v>
+        <v>18360</v>
       </c>
       <c r="F4">
-        <v>3814.2</v>
+        <v>4932</v>
       </c>
       <c r="G4">
-        <v>0.26938268888003197</v>
+        <v>0.24483675340362801</v>
       </c>
       <c r="I4">
-        <v>0.111250452341418</v>
+        <v>0.72834929859255104</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>44886</v>
+        <v>44929</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>21.43</v>
+        <v>21.56</v>
       </c>
       <c r="E5">
-        <v>18678</v>
+        <v>10704</v>
       </c>
       <c r="F5">
-        <v>3814.2</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G5">
-        <v>0.26938268888003197</v>
+        <v>0.256226733839999</v>
       </c>
       <c r="H5">
-        <v>37.438864801751997</v>
+        <v>6.0246525978349297</v>
       </c>
       <c r="I5">
-        <v>0.427275897045924</v>
+        <v>6.5658835581262703E-2</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>44900</v>
+        <v>44929</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>21.76</v>
+        <v>21.56</v>
       </c>
       <c r="E6">
-        <v>10254</v>
+        <v>20454</v>
       </c>
       <c r="F6">
         <v>573.20000000000005</v>
       </c>
       <c r="G6">
-        <v>0.25936577783929399</v>
+        <v>0.256226733839999</v>
       </c>
       <c r="H6">
-        <v>20.707887873600399</v>
+        <v>13.892989272610601</v>
       </c>
       <c r="I6">
-        <v>0.22984039458512301</v>
+        <v>0.15141080478406299</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>44900</v>
+        <v>44914</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>21.76</v>
+        <v>19.760000000000002</v>
       </c>
       <c r="E7">
-        <v>17610</v>
+        <v>14358</v>
       </c>
       <c r="F7">
-        <v>573.20000000000005</v>
+        <v>4272.6000000000004</v>
       </c>
       <c r="G7">
-        <v>0.25936577783929399</v>
+        <v>0.25705820430833598</v>
       </c>
       <c r="H7">
-        <v>20.5111754182536</v>
+        <v>20.528070790228</v>
       </c>
       <c r="I7">
-        <v>0.22765704934814299</v>
+        <v>0.21232712840356199</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -4822,82 +5740,88 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8">
         <v>19.760000000000002</v>
       </c>
       <c r="E8">
-        <v>14358</v>
+        <v>19158</v>
       </c>
       <c r="F8">
         <v>4272.6000000000004</v>
       </c>
       <c r="G8">
-        <v>0.24779631643734701</v>
+        <v>0.25705820430833598</v>
       </c>
       <c r="H8">
-        <v>21.29534890235</v>
+        <v>22.590230949448301</v>
       </c>
       <c r="I8">
-        <v>0.21232712840356199</v>
+        <v>0.23365658256366301</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>44914</v>
+        <v>44900</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9">
-        <v>19.760000000000002</v>
+        <v>21.76</v>
       </c>
       <c r="E9">
-        <v>19158</v>
+        <v>10254</v>
       </c>
       <c r="F9">
-        <v>4272.6000000000004</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G9">
-        <v>0.24779631643734701</v>
+        <v>0.25846925292986</v>
       </c>
       <c r="H9">
-        <v>23.4345864630479</v>
+        <v>20.779715129995601</v>
       </c>
       <c r="I9">
-        <v>0.23365658256366301</v>
+        <v>0.22984039458512301</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>44929</v>
+        <v>44900</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10">
-        <v>21.56</v>
+        <v>21.76</v>
       </c>
       <c r="E10">
-        <v>10704</v>
+        <v>17610</v>
       </c>
       <c r="F10">
         <v>573.20000000000005</v>
       </c>
+      <c r="G10">
+        <v>0.25846925292986</v>
+      </c>
+      <c r="H10">
+        <v>20.582320358999102</v>
+      </c>
       <c r="I10">
-        <v>6.5658835581262703E-2</v>
+        <v>0.22765704934814299</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>44972</v>
+        <v>44886</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -4906,24 +5830,27 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>14.42</v>
+        <v>21.43</v>
       </c>
       <c r="E11">
-        <v>23832</v>
+        <v>20514</v>
       </c>
       <c r="F11">
-        <v>2506.1999999999998</v>
+        <v>3814.2</v>
       </c>
       <c r="G11">
-        <v>1.6052859302193001</v>
+        <v>0.26494909806747902</v>
+      </c>
+      <c r="H11">
+        <v>9.9111329260555596</v>
       </c>
       <c r="I11">
-        <v>2.4799278587846699E-2</v>
+        <v>0.111250452341418</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>44972</v>
+        <v>44886</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -4932,24 +5859,24 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>14.42</v>
+        <v>21.43</v>
       </c>
       <c r="E12">
-        <v>18936</v>
+        <v>18678</v>
       </c>
       <c r="F12">
-        <v>2506.1999999999998</v>
+        <v>3814.2</v>
       </c>
       <c r="G12">
-        <v>1.6052859302193001</v>
+        <v>0.26494909806747902</v>
       </c>
       <c r="I12">
-        <v>3.14351431512985E-2</v>
+        <v>0.427275897045924</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>45028</v>
+        <v>44886</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
@@ -4958,85 +5885,79 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>20.99</v>
+        <v>21.43</v>
       </c>
       <c r="E13">
-        <v>22224</v>
+        <v>21006</v>
       </c>
       <c r="F13">
-        <v>7206</v>
+        <v>4236.6000000000004</v>
       </c>
       <c r="G13">
-        <v>0.73846124410021996</v>
+        <v>0.26502797555140301</v>
       </c>
       <c r="H13">
-        <v>5.4632456631712998</v>
+        <v>10.1577577965675</v>
       </c>
       <c r="I13">
-        <v>0.168634803961631</v>
+        <v>0.114052710685128</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>45028</v>
+        <v>44872</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14">
-        <v>20.99</v>
+        <v>10</v>
+      </c>
+      <c r="D14" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E14">
-        <v>22974</v>
+        <v>1798.8</v>
       </c>
       <c r="F14">
-        <v>7206</v>
+        <v>1182.0619999999999</v>
       </c>
       <c r="G14">
-        <v>0.73846124410021996</v>
-      </c>
-      <c r="H14">
-        <v>2.1537714224900602</v>
-      </c>
-      <c r="I14">
-        <v>6.6480777911594499E-2</v>
+        <v>0.26658216225721099</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>45028</v>
+        <v>45050</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15">
-        <v>20.99</v>
+        <v>22.26</v>
       </c>
       <c r="E15">
-        <v>21384</v>
+        <v>21510</v>
       </c>
       <c r="F15">
-        <v>7236</v>
+        <v>5358</v>
       </c>
       <c r="G15">
-        <v>0.73639287530589403</v>
+        <v>0.32557883548586403</v>
       </c>
       <c r="H15">
-        <v>2.1639379833854999</v>
+        <v>25.708252717455</v>
       </c>
       <c r="I15">
-        <v>6.6607504518364599E-2</v>
+        <v>0.36364535366281198</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>45042</v>
+        <v>45050</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -5045,27 +5966,27 @@
         <v>10</v>
       </c>
       <c r="D16">
-        <v>21.64</v>
+        <v>22.26</v>
       </c>
       <c r="E16">
-        <v>24588</v>
+        <v>23946</v>
       </c>
       <c r="F16">
-        <v>573.20000000000005</v>
+        <v>5406</v>
       </c>
       <c r="G16">
-        <v>0.352445767303255</v>
+        <v>0.32700939804183699</v>
       </c>
       <c r="H16">
-        <v>7.0894276044164304</v>
+        <v>25.6620546637158</v>
       </c>
       <c r="I16">
-        <v>0.10653628208794499</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.364586830306599</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>45050</v>
+        <v>45042</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
@@ -5074,27 +5995,27 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>22.26</v>
+        <v>21.64</v>
       </c>
       <c r="E17">
-        <v>23946</v>
+        <v>23790</v>
       </c>
       <c r="F17">
-        <v>5406</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G17">
-        <v>0.34979625322111801</v>
+        <v>0.35825069383838998</v>
       </c>
       <c r="H17">
-        <v>23.990345725040498</v>
+        <v>6.9745538382867203</v>
       </c>
       <c r="I17">
-        <v>0.364586830306599</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.10653628208794499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>45050</v>
+        <v>45042</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -5103,27 +6024,27 @@
         <v>10</v>
       </c>
       <c r="D18">
-        <v>22.26</v>
+        <v>21.64</v>
       </c>
       <c r="E18">
-        <v>21510</v>
+        <v>24588</v>
       </c>
       <c r="F18">
-        <v>5358</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G18">
-        <v>0.34624235777991702</v>
+        <v>0.35891220134342799</v>
       </c>
       <c r="H18">
-        <v>24.1740006502773</v>
+        <v>6.9616991075446499</v>
       </c>
       <c r="I18">
-        <v>0.36364535366281198</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.10653628208794499</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>45064</v>
+        <v>44944</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
@@ -5132,141 +6053,441 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>21.72</v>
+        <v>21.15</v>
       </c>
       <c r="E19">
-        <v>24084</v>
+        <v>15744</v>
       </c>
       <c r="F19">
-        <v>4387.2</v>
+        <v>4738.8</v>
       </c>
       <c r="G19">
-        <v>0.236309150486498</v>
+        <v>0.36459096455608803</v>
       </c>
       <c r="H19">
-        <v>21.6709643391052</v>
+        <v>16.279117207498601</v>
       </c>
       <c r="I19">
-        <v>0.21888147684550499</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.24930788677166099</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>45075</v>
+        <v>44944</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20">
-        <v>21.49</v>
+        <v>21.15</v>
       </c>
       <c r="E20">
-        <v>16446</v>
+        <v>18324</v>
       </c>
       <c r="F20">
-        <v>573.20000000000005</v>
+        <v>4738.8</v>
       </c>
       <c r="G20">
-        <v>0.41818901391054503</v>
+        <v>0.36459096455608803</v>
       </c>
       <c r="H20">
-        <v>6.7191684375126197</v>
+        <v>21.051811488658899</v>
       </c>
       <c r="I20">
-        <v>0.119261080090433</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.322399708046537</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>45075</v>
+        <v>44944</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21">
-        <v>21.49</v>
+        <v>21.15</v>
       </c>
       <c r="E21">
-        <v>23496</v>
+        <v>21438</v>
       </c>
       <c r="F21">
-        <v>573.20000000000005</v>
+        <v>5010</v>
       </c>
       <c r="G21">
-        <v>0.41485994116438002</v>
+        <v>0.36465776923577697</v>
       </c>
       <c r="H21">
-        <v>10.6037922821831</v>
+        <v>16.544827851223001</v>
       </c>
       <c r="I21">
-        <v>0.18671246119286999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.25342356116248699</v>
+      </c>
+      <c r="K21">
+        <f>AVERAGE(H2:H23)</f>
+        <v>15.699331506482597</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>45086</v>
+        <v>45075</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>22.22</v>
+        <v>21.49</v>
       </c>
       <c r="E22">
-        <v>22506</v>
+        <v>23496</v>
       </c>
       <c r="F22">
-        <v>4932</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G22">
-        <v>0.245623597499528</v>
+        <v>0.41010863057300501</v>
       </c>
       <c r="H22">
-        <v>42.991528895930301</v>
+        <v>10.726642441441401</v>
       </c>
       <c r="I22">
-        <v>0.458224391330884</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.18671246119286999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>45086</v>
+        <v>45075</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>21.49</v>
+      </c>
+      <c r="E23">
+        <v>16446</v>
+      </c>
+      <c r="F23">
+        <v>573.20000000000005</v>
+      </c>
+      <c r="G23">
+        <v>0.41065339316936</v>
+      </c>
+      <c r="H23">
+        <v>6.8424673213972902</v>
+      </c>
+      <c r="I23">
+        <v>0.119261080090433</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
         <v>11</v>
       </c>
-      <c r="D23">
-        <v>22.22</v>
-      </c>
-      <c r="E23">
-        <v>18360</v>
-      </c>
-      <c r="F23">
-        <v>4932</v>
-      </c>
-      <c r="G23">
-        <v>0.245623597499528</v>
-      </c>
-      <c r="H23">
-        <v>68.335187975973895</v>
-      </c>
-      <c r="I23">
-        <v>0.72834929859255104</v>
+      <c r="D24">
+        <v>20.99</v>
+      </c>
+      <c r="E24">
+        <v>21384</v>
+      </c>
+      <c r="F24">
+        <v>7236</v>
+      </c>
+      <c r="G24">
+        <v>0.73861822689876599</v>
+      </c>
+      <c r="H24">
+        <v>2.1574183462267702</v>
+      </c>
+      <c r="I24">
+        <v>6.6607504518364599E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25">
+        <v>20.99</v>
+      </c>
+      <c r="E25">
+        <v>22224</v>
+      </c>
+      <c r="F25">
+        <v>7206</v>
+      </c>
+      <c r="G25">
+        <v>0.73935259974152701</v>
+      </c>
+      <c r="H25">
+        <v>5.4566592322269702</v>
+      </c>
+      <c r="I25">
+        <v>0.168634803961631</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>45028</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>20.99</v>
+      </c>
+      <c r="E26">
+        <v>22974</v>
+      </c>
+      <c r="F26">
+        <v>7206</v>
+      </c>
+      <c r="G26">
+        <v>0.73935259974152701</v>
+      </c>
+      <c r="H26">
+        <v>2.1511748585391199</v>
+      </c>
+      <c r="I26">
+        <v>6.6480777911594499E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>45014</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27">
+        <v>20.91</v>
+      </c>
+      <c r="E27">
+        <v>22506</v>
+      </c>
+      <c r="F27">
+        <v>7740</v>
+      </c>
+      <c r="G27">
+        <v>0.88614433356157496</v>
+      </c>
+      <c r="H27">
+        <v>2.8211227677034598</v>
+      </c>
+      <c r="I27">
+        <v>0.104238501087662</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>45014</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>20.91</v>
+      </c>
+      <c r="E28">
+        <v>24660</v>
+      </c>
+      <c r="F28">
+        <v>7740</v>
+      </c>
+      <c r="G28">
+        <v>0.88614433356157496</v>
+      </c>
+      <c r="H28">
+        <v>2.1187175452266498</v>
+      </c>
+      <c r="I28">
+        <v>7.8285122388467202E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>45014</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>20.91</v>
+      </c>
+      <c r="E29">
+        <v>22350</v>
+      </c>
+      <c r="F29">
+        <v>7650</v>
+      </c>
+      <c r="G29">
+        <v>0.88741132439375403</v>
+      </c>
+      <c r="H29">
+        <v>2.1044984311737398</v>
+      </c>
+      <c r="I29">
+        <v>7.7870915391702794E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>44958</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30">
+        <v>21.22</v>
+      </c>
+      <c r="E30">
+        <v>24930</v>
+      </c>
+      <c r="F30">
+        <v>6594</v>
+      </c>
+      <c r="G30">
+        <v>0.94276859487791098</v>
+      </c>
+      <c r="H30">
+        <v>1.3105955732377901</v>
+      </c>
+      <c r="I30">
+        <v>5.2012010255559397E-2</v>
+      </c>
+      <c r="O30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>44958</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>21.22</v>
+      </c>
+      <c r="E31">
+        <v>18420</v>
+      </c>
+      <c r="F31">
+        <v>6594</v>
+      </c>
+      <c r="G31">
+        <v>0.94276859487791098</v>
+      </c>
+      <c r="H31">
+        <v>1.36490590126142</v>
+      </c>
+      <c r="I31">
+        <v>5.4167358095754702E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>44972</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32">
+        <v>14.42</v>
+      </c>
+      <c r="E32">
+        <v>23832</v>
+      </c>
+      <c r="F32">
+        <v>2506.1999999999998</v>
+      </c>
+      <c r="G32">
+        <v>1.60103975950207</v>
+      </c>
+      <c r="H32">
+        <v>0.45773182901047699</v>
+      </c>
+      <c r="I32">
+        <v>2.4799278587846699E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>44972</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33">
+        <v>14.42</v>
+      </c>
+      <c r="E33">
+        <v>18936</v>
+      </c>
+      <c r="F33">
+        <v>2506.1999999999998</v>
+      </c>
+      <c r="G33">
+        <v>1.60103975950207</v>
+      </c>
+      <c r="H33">
+        <v>0.58021307026655</v>
+      </c>
+      <c r="I33">
+        <v>3.14351431512985E-2</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I34">
+    <sortCondition ref="G2:G34"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
@@ -5275,7 +6496,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5309,160 +6530,181 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>44858</v>
+        <v>45064</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>22.74</v>
+        <v>22.71</v>
       </c>
       <c r="E2">
-        <v>77.099999999999994</v>
+        <v>26580</v>
       </c>
       <c r="F2">
-        <v>6772.2275483438798</v>
+        <v>5640.0318337175104</v>
       </c>
       <c r="G2">
-        <v>0.56928417135890497</v>
+        <v>0.39570458731269098</v>
+      </c>
+      <c r="H2">
+        <v>10.088633653432099</v>
       </c>
       <c r="I2">
-        <v>-3.4953103252217102E-5</v>
+        <v>0.175804478721235</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>44872</v>
+        <v>45064</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>22.84</v>
+        <v>22.71</v>
       </c>
       <c r="E3">
-        <v>15990</v>
+        <v>24990</v>
       </c>
       <c r="F3">
-        <v>6522.0305392485297</v>
+        <v>5433.1613828108102</v>
       </c>
       <c r="G3">
-        <v>0.53624716455618304</v>
+        <v>0.395724677442572</v>
+      </c>
+      <c r="H3">
+        <v>9.9894337092864802</v>
       </c>
       <c r="I3">
-        <v>0.59945886197372</v>
+        <v>0.174084658920136</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>44886</v>
+        <v>45075</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>22.2</v>
+        <v>22.34</v>
       </c>
       <c r="E4">
-        <v>24432</v>
+        <v>16692</v>
       </c>
       <c r="F4">
-        <v>5983.8444990745702</v>
+        <v>5473.2343954034995</v>
       </c>
       <c r="G4">
-        <v>0.55202433267831497</v>
+        <v>0.41314429687603998</v>
+      </c>
+      <c r="H4">
+        <v>10.818929035817799</v>
       </c>
       <c r="I4">
-        <v>0.53304964088052798</v>
+        <v>0.194662682442417</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>44886</v>
+        <v>45042</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="E5">
-        <v>23322</v>
+        <v>20490</v>
       </c>
       <c r="F5">
-        <v>5916.7378643532802</v>
+        <v>5622.7792873607596</v>
       </c>
       <c r="G5">
-        <v>0.55215372043341704</v>
+        <v>0.41420772624117003</v>
+      </c>
+      <c r="H5">
+        <v>16.7661132110034</v>
       </c>
       <c r="I5">
-        <v>0.53111765810454403</v>
+        <v>0.30208121634153201</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>44900</v>
+        <v>45042</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E6">
-        <v>17220</v>
+        <v>23160</v>
       </c>
       <c r="F6">
-        <v>6562.7722472662899</v>
+        <v>5679.94985068187</v>
       </c>
       <c r="G6">
-        <v>0.53038484152501797</v>
+        <v>0.41427437299901998</v>
+      </c>
+      <c r="H6">
+        <v>16.818242674381999</v>
       </c>
       <c r="I6">
-        <v>0.20549062678525201</v>
+        <v>0.30306920854747199</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>44915</v>
+        <v>45028</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>21.02</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E7">
-        <v>20532</v>
+        <v>18822</v>
       </c>
       <c r="F7">
-        <v>573.20000000000005</v>
+        <v>5600.2851635686502</v>
+      </c>
+      <c r="G7">
+        <v>0.437729121568594</v>
+      </c>
+      <c r="H7">
+        <v>16.428025299675401</v>
       </c>
       <c r="I7">
-        <v>7.5136667138173505E-2</v>
+        <v>0.27017532655438897</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>44929</v>
+        <v>44972</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -5471,27 +6713,27 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>21.67</v>
+        <v>21.03</v>
       </c>
       <c r="E8">
-        <v>19458</v>
+        <v>23880</v>
       </c>
       <c r="F8">
-        <v>6107.8958463442596</v>
+        <v>5772.5353821522203</v>
       </c>
       <c r="G8">
-        <v>0.49738770877387101</v>
+        <v>0.47310841336748199</v>
       </c>
       <c r="H8">
-        <v>4.0402645513699502</v>
+        <v>9.6476919720071006</v>
       </c>
       <c r="I8">
-        <v>8.5762042866372595E-2</v>
+        <v>0.19102312806001301</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>44929</v>
+        <v>44972</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -5500,85 +6742,85 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>21.67</v>
+        <v>21.03</v>
       </c>
       <c r="E9">
-        <v>9744</v>
+        <v>23736</v>
       </c>
       <c r="F9">
-        <v>6017.3477409245197</v>
+        <v>5684.7840110370498</v>
       </c>
       <c r="G9">
-        <v>0.50010485163101304</v>
+        <v>0.473199183951164</v>
       </c>
       <c r="H9">
-        <v>3.9921305911887899</v>
+        <v>9.5993216311403806</v>
       </c>
       <c r="I9">
-        <v>8.5203232704493106E-2</v>
+        <v>0.19010186714109101</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>44944</v>
+        <v>44972</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10">
-        <v>21.84</v>
+        <v>21.03</v>
       </c>
       <c r="E10">
-        <v>21330</v>
+        <v>15306</v>
       </c>
       <c r="F10">
-        <v>5588.1246494146499</v>
+        <v>5684.7840110370498</v>
       </c>
       <c r="G10">
-        <v>0.50066878710324902</v>
+        <v>0.473199183951164</v>
       </c>
       <c r="H10">
-        <v>5.9088682106652497</v>
+        <v>8.3328428116839692</v>
       </c>
       <c r="I10">
-        <v>0.126907453227872</v>
+        <v>0.16502092939104501</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>44944</v>
+        <v>45000</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11">
-        <v>21.84</v>
+        <v>19.420000000000002</v>
       </c>
       <c r="E11">
-        <v>17196</v>
+        <v>22194</v>
       </c>
       <c r="F11">
-        <v>5588.1246494146499</v>
+        <v>5604.25032645599</v>
       </c>
       <c r="G11">
-        <v>0.50066878710324902</v>
+        <v>0.486286253704515</v>
       </c>
       <c r="H11">
-        <v>5.8149297981260997</v>
+        <v>7.8022981892533503</v>
       </c>
       <c r="I11">
-        <v>0.124889895165891</v>
+        <v>0.151048107990056</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>44958</v>
+        <v>45000</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -5587,22 +6829,22 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>21.04</v>
+        <v>19.420000000000002</v>
       </c>
       <c r="E12">
-        <v>24576</v>
+        <v>21306</v>
       </c>
       <c r="F12">
-        <v>5774.7404078712798</v>
+        <v>5530.1392519331903</v>
       </c>
       <c r="G12">
-        <v>0.49134635833564899</v>
+        <v>0.48686892584765001</v>
       </c>
       <c r="H12">
-        <v>8.2302959995820704</v>
+        <v>7.7583020845305404</v>
       </c>
       <c r="I12">
-        <v>0.16929271518545699</v>
+        <v>0.15037633463830899</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -5613,59 +6855,59 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>21.04</v>
       </c>
       <c r="E13">
-        <v>18120</v>
+        <v>24576</v>
       </c>
       <c r="F13">
         <v>5774.7404078712798</v>
       </c>
       <c r="G13">
-        <v>0.49134635833564899</v>
+        <v>0.492752758154543</v>
       </c>
       <c r="H13">
-        <v>9.7963568543513109</v>
+        <v>8.2068053410079695</v>
       </c>
       <c r="I13">
-        <v>0.20150573574547101</v>
+        <v>0.16929271518545699</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>44972</v>
+        <v>44958</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14">
-        <v>21.03</v>
+        <v>21.04</v>
       </c>
       <c r="E14">
-        <v>23880</v>
+        <v>18120</v>
       </c>
       <c r="F14">
-        <v>5772.5353821522203</v>
+        <v>5774.7404078712798</v>
       </c>
       <c r="G14">
-        <v>0.48569479876279598</v>
+        <v>0.492752758154543</v>
       </c>
       <c r="H14">
-        <v>9.39767988696053</v>
+        <v>9.7683963928870696</v>
       </c>
       <c r="I14">
-        <v>0.19102312806001301</v>
+        <v>0.20150573574547101</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>44972</v>
+        <v>44929</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -5674,114 +6916,114 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>21.03</v>
+        <v>21.7</v>
       </c>
       <c r="E15">
-        <v>23736</v>
+        <v>19458</v>
       </c>
       <c r="F15">
-        <v>5684.7840110370498</v>
+        <v>6107.8958463442596</v>
       </c>
       <c r="G15">
-        <v>0.48888636338864599</v>
+        <v>0.497716180087658</v>
       </c>
       <c r="H15">
-        <v>9.2913026472153</v>
+        <v>4.03684971713494</v>
       </c>
       <c r="I15">
-        <v>0.19010186714109101</v>
+        <v>8.5824373596079695E-2</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>44972</v>
+        <v>44929</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>21.03</v>
+        <v>21.7</v>
       </c>
       <c r="E16">
-        <v>15306</v>
+        <v>9744</v>
       </c>
       <c r="F16">
-        <v>5684.7840110370498</v>
+        <v>6017.3477409245197</v>
       </c>
       <c r="G16">
-        <v>0.48888636338864599</v>
+        <v>0.49773357358562098</v>
       </c>
       <c r="H16">
-        <v>8.0654620659721097</v>
+        <v>4.0104061748601199</v>
       </c>
       <c r="I16">
-        <v>0.16502092939104501</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>8.5265157298292205E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>44986</v>
+        <v>44929</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="E17">
-        <v>19626</v>
+        <v>18030</v>
       </c>
       <c r="F17">
-        <v>6021.9090408438997</v>
+        <v>6017.3477409245197</v>
       </c>
       <c r="G17">
-        <v>0.46564457952216998</v>
+        <v>0.49773357358562098</v>
       </c>
       <c r="H17">
-        <v>6.4953401493818799</v>
+        <v>10.530608571701499</v>
       </c>
       <c r="I17">
-        <v>0.129587075886479</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.22389103675868699</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>44986</v>
+        <v>44944</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18">
-        <v>21.8</v>
+        <v>21.84</v>
       </c>
       <c r="E18">
-        <v>19632</v>
+        <v>21330</v>
       </c>
       <c r="F18">
-        <v>6021.9090408438997</v>
+        <v>5588.1246494146499</v>
       </c>
       <c r="G18">
-        <v>0.46564457952216998</v>
+        <v>0.49782071547936002</v>
       </c>
       <c r="H18">
-        <v>5.2541923592863702</v>
+        <v>5.9426733122948399</v>
       </c>
       <c r="I18">
-        <v>0.104825214434658</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.126907453227872</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>44986</v>
+        <v>44944</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -5790,201 +7032,190 @@
         <v>11</v>
       </c>
       <c r="D19">
-        <v>21.8</v>
+        <v>21.84</v>
       </c>
       <c r="E19">
-        <v>18780</v>
+        <v>17196</v>
       </c>
       <c r="F19">
-        <v>5837.03059602348</v>
+        <v>5588.1246494146499</v>
       </c>
       <c r="G19">
-        <v>0.46503914239829702</v>
+        <v>0.49782071547936002</v>
       </c>
       <c r="H19">
-        <v>5.1905251222689399</v>
+        <v>5.8481974706796702</v>
       </c>
       <c r="I19">
-        <v>0.103420360095724</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.124889895165891</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>45000</v>
+        <v>44915</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20">
-        <v>19.420000000000002</v>
+        <v>21.02</v>
       </c>
       <c r="E20">
-        <v>22194</v>
+        <v>20532</v>
       </c>
       <c r="F20">
-        <v>5604.25032645599</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G20">
-        <v>0.489100382047087</v>
+        <v>0.512233193314514</v>
       </c>
       <c r="H20">
-        <v>7.7574062421653602</v>
+        <v>3.5060297572933301</v>
       </c>
       <c r="I20">
-        <v>0.151048107990056</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>7.5136667138173505E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>45000</v>
+        <v>44900</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <v>19.420000000000002</v>
+        <v>22.4</v>
       </c>
       <c r="E21">
-        <v>21306</v>
+        <v>17220</v>
       </c>
       <c r="F21">
-        <v>5530.1392519331903</v>
+        <v>6562.7722472662899</v>
       </c>
       <c r="G21">
-        <v>0.482196446574851</v>
+        <v>0.52959181897001695</v>
       </c>
       <c r="H21">
-        <v>7.8334799626330902</v>
+        <v>8.8934299493761699</v>
       </c>
       <c r="I21">
-        <v>0.15037633463830899</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.20549062678525201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>45028</v>
+        <v>44872</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>17.600000000000001</v>
+        <v>22.84</v>
       </c>
       <c r="E22">
-        <v>18822</v>
+        <v>15990</v>
       </c>
       <c r="F22">
-        <v>5600.2851635686502</v>
+        <v>6522.0305392485297</v>
       </c>
       <c r="G22">
-        <v>0.44955411343768997</v>
-      </c>
-      <c r="H22">
-        <v>15.995905428480199</v>
+        <v>0.53593698976396698</v>
       </c>
       <c r="I22">
-        <v>0.27017532655438897</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.59945886197372</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>45042</v>
+        <v>44886</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D23">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="E23">
-        <v>23160</v>
+        <v>23322</v>
       </c>
       <c r="F23">
-        <v>5679.94985068187</v>
+        <v>5916.7378643532802</v>
       </c>
       <c r="G23">
-        <v>0.43002307281753499</v>
-      </c>
-      <c r="H23">
-        <v>16.2023095487049</v>
+        <v>0.55030838061051701</v>
       </c>
       <c r="I23">
-        <v>0.30306920854747199</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.53111765810454403</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>45042</v>
+        <v>44886</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="E24">
-        <v>20490</v>
+        <v>24432</v>
       </c>
       <c r="F24">
-        <v>5622.7792873607596</v>
+        <v>5983.8444990745702</v>
       </c>
       <c r="G24">
-        <v>0.42251695542155299</v>
-      </c>
-      <c r="H24">
-        <v>16.4363904026123</v>
+        <v>0.550502530962522</v>
       </c>
       <c r="I24">
-        <v>0.30208121634153201</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.53304964088052798</v>
+      </c>
+      <c r="K24">
+        <f>AVERAGE(H2:H21)</f>
+        <v>9.2396615479724069</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>45064</v>
+        <v>44858</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25">
-        <v>22.71</v>
+        <v>22.74</v>
       </c>
       <c r="E25">
-        <v>26580</v>
+        <v>77.099999999999994</v>
       </c>
       <c r="F25">
-        <v>5640.0318337175104</v>
+        <v>6772.2275483438798</v>
       </c>
       <c r="G25">
-        <v>0.41031788759051402</v>
-      </c>
-      <c r="H25">
-        <v>9.7293311774023596</v>
-      </c>
-      <c r="I25">
-        <v>0.175804478721235</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.56969572112081401</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>45064</v>
+        <v>44986</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
@@ -5993,54 +7224,22 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>22.71</v>
+        <v>21.8</v>
       </c>
       <c r="E26">
-        <v>24990</v>
+        <v>19626</v>
       </c>
       <c r="F26">
-        <v>5433.1613828108102</v>
-      </c>
-      <c r="G26">
-        <v>0.40721095386800199</v>
-      </c>
-      <c r="H26">
-        <v>9.7076598625162198</v>
+        <v>6021.9090408438997</v>
       </c>
       <c r="I26">
-        <v>0.174084658920136</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>45075</v>
-      </c>
-      <c r="B27" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27">
-        <v>22.34</v>
-      </c>
-      <c r="E27">
-        <v>16692</v>
-      </c>
-      <c r="F27">
-        <v>5473.2343954034995</v>
-      </c>
-      <c r="G27">
-        <v>0.431708368833988</v>
-      </c>
-      <c r="H27">
-        <v>10.353699747649699</v>
-      </c>
-      <c r="I27">
-        <v>0.194662682442417</v>
+        <v>0.129587075886479</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I26">
+    <sortCondition ref="G2:G26"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
@@ -6049,7 +7248,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6083,7 +7282,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>44872</v>
+        <v>44929</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -6092,27 +7291,27 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>22.52</v>
+        <v>21.12</v>
       </c>
       <c r="E2">
-        <v>7758</v>
+        <v>15816</v>
       </c>
       <c r="F2">
         <v>573.20000000000005</v>
       </c>
       <c r="G2">
-        <v>0.99589610999220601</v>
+        <v>0.88949597204892406</v>
       </c>
       <c r="H2">
-        <v>3.6359854222587802</v>
+        <v>3.1998276591435801</v>
       </c>
       <c r="I2">
-        <v>0.15855698156709899</v>
+        <v>0.119445760939699</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>44886</v>
+        <v>45075</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -6121,27 +7320,27 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <v>20.48</v>
+        <v>22.92</v>
       </c>
       <c r="E3">
-        <v>19086</v>
+        <v>20580</v>
       </c>
       <c r="F3">
-        <v>573.20000000000005</v>
+        <v>3104.7972</v>
       </c>
       <c r="G3">
-        <v>0.97722836908240696</v>
+        <v>0.89694420076360204</v>
       </c>
       <c r="H3">
-        <v>7.4659573982030203</v>
+        <v>5.2067473398202804</v>
       </c>
       <c r="I3">
-        <v>0.30021111601335398</v>
+        <v>0.20696150256924101</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>44900</v>
+        <v>44914</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -6150,27 +7349,27 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>21.5</v>
+        <v>19.48</v>
       </c>
       <c r="E4">
-        <v>19572</v>
+        <v>19158</v>
       </c>
       <c r="F4">
         <v>573.20000000000005</v>
       </c>
       <c r="G4">
-        <v>0.94090301323553105</v>
+        <v>0.89966739347265001</v>
       </c>
       <c r="H4">
-        <v>3.2336938360616001</v>
+        <v>3.6055235509349699</v>
       </c>
       <c r="I4">
-        <v>0.12917745061024599</v>
+        <v>0.129380530943568</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>44914</v>
+        <v>44944</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -6179,27 +7378,27 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>19.48</v>
+        <v>20.88</v>
       </c>
       <c r="E5">
-        <v>19158</v>
+        <v>18366</v>
       </c>
       <c r="F5">
-        <v>573.20000000000005</v>
+        <v>1118.2565999999999</v>
       </c>
       <c r="G5">
-        <v>0.89966739347265001</v>
+        <v>0.90011033030870202</v>
       </c>
       <c r="H5">
-        <v>3.6055235509349699</v>
+        <v>3.1209961501293702</v>
       </c>
       <c r="I5">
-        <v>0.129380530943568</v>
+        <v>0.117028118053404</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>44929</v>
+        <v>44900</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -6208,27 +7407,27 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>21.12</v>
+        <v>21.5</v>
       </c>
       <c r="E6">
-        <v>15816</v>
+        <v>19572</v>
       </c>
       <c r="F6">
         <v>573.20000000000005</v>
       </c>
       <c r="G6">
-        <v>0.88949597204892406</v>
+        <v>0.94090301323553105</v>
       </c>
       <c r="H6">
-        <v>3.1998276591435801</v>
+        <v>3.2336938360616001</v>
       </c>
       <c r="I6">
-        <v>0.119445760939699</v>
+        <v>0.12917745061024599</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>44944</v>
+        <v>44886</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
@@ -6237,27 +7436,27 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>20.88</v>
+        <v>20.48</v>
       </c>
       <c r="E7">
-        <v>18366</v>
+        <v>19086</v>
       </c>
       <c r="F7">
-        <v>1118.2565999999999</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G7">
-        <v>0.90011033030870202</v>
+        <v>0.97722836908240696</v>
       </c>
       <c r="H7">
-        <v>3.1209961501293702</v>
+        <v>7.4659573982030203</v>
       </c>
       <c r="I7">
-        <v>0.117028118053404</v>
+        <v>0.30021111601335398</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>44958</v>
+        <v>44872</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
@@ -6266,27 +7465,27 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>21.16</v>
+        <v>22.52</v>
       </c>
       <c r="E8">
-        <v>25284</v>
+        <v>7758</v>
       </c>
       <c r="F8">
-        <v>1726.434</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G8">
-        <v>1.2366864918379299</v>
+        <v>0.99589610999220601</v>
       </c>
       <c r="H8">
-        <v>2.1878451594958102</v>
+        <v>3.6359854222587802</v>
       </c>
       <c r="I8">
-        <v>0.113686385875942</v>
+        <v>0.15855698156709899</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>44972</v>
+        <v>45042</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -6295,24 +7494,27 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>20.02</v>
+        <v>21.3</v>
       </c>
       <c r="E9">
-        <v>16248</v>
+        <v>22278</v>
       </c>
       <c r="F9">
-        <v>573.20000000000005</v>
+        <v>3241.6116000000002</v>
       </c>
       <c r="G9">
-        <v>1.85747687368365</v>
+        <v>1.0442543706910099</v>
+      </c>
+      <c r="H9">
+        <v>4.6176963145351104</v>
       </c>
       <c r="I9">
-        <v>0.31615444563082801</v>
+        <v>0.203481011201437</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>44986</v>
+        <v>44958</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
@@ -6321,27 +7523,27 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>21.54</v>
+        <v>21.16</v>
       </c>
       <c r="E10">
-        <v>19032</v>
+        <v>25284</v>
       </c>
       <c r="F10">
-        <v>573.20000000000005</v>
+        <v>1726.434</v>
       </c>
       <c r="G10">
-        <v>2.4218717197483</v>
+        <v>1.2366864918379299</v>
       </c>
       <c r="H10">
-        <v>1.01033184827849</v>
+        <v>2.1878451594958102</v>
       </c>
       <c r="I10">
-        <v>0.104012943753354</v>
+        <v>0.113686385875942</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>45000</v>
+        <v>45028</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
@@ -6350,27 +7552,27 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>19.760000000000002</v>
+        <v>20.9</v>
       </c>
       <c r="E11">
-        <v>24492</v>
+        <v>18072</v>
       </c>
       <c r="F11">
-        <v>3347.7624000000001</v>
+        <v>3180.7955999999999</v>
       </c>
       <c r="G11">
-        <v>1.71905533629398</v>
+        <v>1.4229669796427999</v>
       </c>
       <c r="H11">
-        <v>2.3123306997931201</v>
+        <v>6.3531601948909397</v>
       </c>
       <c r="I11">
-        <v>0.15994316366882999</v>
+        <v>0.37683641747636698</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>45014</v>
+        <v>45028</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -6379,24 +7581,27 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>21.16</v>
+        <v>20.9</v>
       </c>
       <c r="E12">
-        <v>17646</v>
+        <v>23370</v>
       </c>
       <c r="F12">
-        <v>3604.5306</v>
+        <v>3165.6414</v>
       </c>
       <c r="G12">
-        <v>1.6347916457732701</v>
+        <v>1.4304669796428</v>
+      </c>
+      <c r="H12">
+        <v>6.3151101233337998</v>
       </c>
       <c r="I12">
-        <v>0.26715501908250799</v>
+        <v>0.37655377279801899</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>45028</v>
+        <v>45014</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
@@ -6405,24 +7610,27 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>20.9</v>
+        <v>21.16</v>
       </c>
       <c r="E13">
-        <v>23370</v>
+        <v>17646</v>
       </c>
       <c r="F13">
-        <v>3165.6414</v>
+        <v>3604.5306</v>
       </c>
       <c r="G13">
-        <v>1.43046697964281</v>
+        <v>1.6347916457732701</v>
+      </c>
+      <c r="H13">
+        <v>3.8892751359493398</v>
       </c>
       <c r="I13">
-        <v>0.37655377279801899</v>
+        <v>0.26715501908250799</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>45028</v>
+        <v>45000</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
@@ -6431,24 +7639,27 @@
         <v>10</v>
       </c>
       <c r="D14">
-        <v>20.9</v>
+        <v>19.760000000000002</v>
       </c>
       <c r="E14">
-        <v>18072</v>
+        <v>24492</v>
       </c>
       <c r="F14">
-        <v>3180.7955999999999</v>
+        <v>3347.7624000000001</v>
       </c>
       <c r="G14">
-        <v>1.4229669796428099</v>
+        <v>1.71905533629398</v>
+      </c>
+      <c r="H14">
+        <v>2.3123306997931201</v>
       </c>
       <c r="I14">
-        <v>0.37683641747636698</v>
+        <v>0.15994316366882999</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>45042</v>
+        <v>44972</v>
       </c>
       <c r="B15" t="s">
         <v>1</v>
@@ -6457,27 +7668,27 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>21.3</v>
+        <v>20.02</v>
       </c>
       <c r="E15">
-        <v>22278</v>
+        <v>16248</v>
       </c>
       <c r="F15">
-        <v>3241.6116000000002</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G15">
-        <v>1.0442543706910099</v>
+        <v>1.85747687368365</v>
       </c>
       <c r="H15">
-        <v>4.6176963145351202</v>
+        <v>4.1959327736538397</v>
       </c>
       <c r="I15">
-        <v>0.203481011201437</v>
+        <v>0.31615444563082801</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>45075</v>
+        <v>44986</v>
       </c>
       <c r="B16" t="s">
         <v>1</v>
@@ -6486,25 +7697,34 @@
         <v>10</v>
       </c>
       <c r="D16">
-        <v>22.92</v>
+        <v>21.54</v>
       </c>
       <c r="E16">
-        <v>20580</v>
+        <v>19032</v>
       </c>
       <c r="F16">
-        <v>3104.7972</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G16">
-        <v>0.89694420076360104</v>
+        <v>2.4218717197483</v>
       </c>
       <c r="H16">
-        <v>5.2067473398202901</v>
+        <v>1.01033184827849</v>
       </c>
       <c r="I16">
-        <v>0.20696150256924101</v>
+        <v>0.104012943753354</v>
+      </c>
+    </row>
+    <row r="19" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K19">
+        <f>AVERAGE(H2:H12)</f>
+        <v>4.4493221044370239</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I16">
+    <sortCondition ref="G2:G16"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
@@ -6513,7 +7733,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6547,7 +7767,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>44865</v>
+        <v>44937</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -6556,27 +7776,24 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>22.38</v>
+        <v>19.16</v>
       </c>
       <c r="E2">
-        <v>17916</v>
+        <v>18636</v>
       </c>
       <c r="F2">
-        <v>573.20000000000005</v>
+        <v>903</v>
       </c>
       <c r="G2">
-        <v>0.41324602598597798</v>
-      </c>
-      <c r="H2">
-        <v>4.7857105061486997</v>
+        <v>0.232705782824495</v>
       </c>
       <c r="I2">
-        <v>8.6233307127701997E-2</v>
+        <v>0.260812263010191</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>44879</v>
+        <v>44907</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -6585,27 +7802,27 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <v>20.88</v>
+        <v>21.58</v>
       </c>
       <c r="E3">
-        <v>18492</v>
+        <v>16464</v>
       </c>
       <c r="F3">
-        <v>1312</v>
+        <v>1458</v>
       </c>
       <c r="G3">
-        <v>0.30467043072306799</v>
+        <v>0.26724465813797499</v>
       </c>
       <c r="H3">
-        <v>22.843809113422701</v>
+        <v>6.6366929502241296</v>
       </c>
       <c r="I3">
-        <v>0.28993461685199901</v>
+        <v>7.5485220817124901E-2</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>44893</v>
+        <v>44879</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -6614,24 +7831,24 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>21.26</v>
+        <v>20.88</v>
       </c>
       <c r="E4">
-        <v>16596</v>
+        <v>18492</v>
       </c>
       <c r="F4">
-        <v>1514</v>
+        <v>1312</v>
       </c>
       <c r="G4">
-        <v>0.445617932445036</v>
+        <v>0.283060203628272</v>
       </c>
       <c r="I4">
-        <v>0.32533250684668602</v>
+        <v>0.28993461685199901</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>44907</v>
+        <v>45076</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -6640,27 +7857,27 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>21.58</v>
+        <v>22.68</v>
       </c>
       <c r="E5">
-        <v>16464</v>
+        <v>19452</v>
       </c>
       <c r="F5">
-        <v>1458</v>
+        <v>1103</v>
       </c>
       <c r="G5">
-        <v>0.36046910737976201</v>
+        <v>0.28406916777292901</v>
       </c>
       <c r="H5">
-        <v>4.9203127323219196</v>
+        <v>10.1472603647596</v>
       </c>
       <c r="I5">
-        <v>7.5485220817124901E-2</v>
+        <v>0.12682610302880001</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>44930</v>
+        <v>45089</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -6669,27 +7886,27 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="E6">
-        <v>22074</v>
+        <v>18408</v>
       </c>
       <c r="F6">
-        <v>1652</v>
+        <v>1260</v>
       </c>
       <c r="G6">
-        <v>0.287405278189796</v>
+        <v>0.29357637887200599</v>
       </c>
       <c r="H6">
-        <v>7.1107619693398103</v>
+        <v>5.2612293332181004</v>
       </c>
       <c r="I6">
-        <v>8.9702364013825406E-2</v>
+        <v>6.7999325636522806E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>44930</v>
+        <v>45063</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -6698,27 +7915,27 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>22.6</v>
+        <v>22.68</v>
       </c>
       <c r="E7">
-        <v>21846</v>
+        <v>26088</v>
       </c>
       <c r="F7">
-        <v>1517</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G7">
-        <v>0.25664809803313798</v>
+        <v>0.30356611946985401</v>
       </c>
       <c r="H7">
-        <v>7.9106353655349597</v>
+        <v>7.56519155189988</v>
       </c>
       <c r="I7">
-        <v>8.91132790723521E-2</v>
+        <v>0.101043637751804</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>44937</v>
+        <v>45049</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -6727,27 +7944,27 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>19.16</v>
+        <v>21.58</v>
       </c>
       <c r="E8">
-        <v>18636</v>
+        <v>17832</v>
       </c>
       <c r="F8">
-        <v>903</v>
+        <v>1433</v>
       </c>
       <c r="G8">
-        <v>0.284917010811369</v>
+        <v>0.30794118768866002</v>
       </c>
       <c r="H8">
-        <v>23.182547856377401</v>
+        <v>10.0391794953904</v>
       </c>
       <c r="I8">
-        <v>0.260812263010191</v>
+        <v>0.13157311940136501</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>44951</v>
+        <v>44865</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -6756,27 +7973,27 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>21.12</v>
+        <v>22.38</v>
       </c>
       <c r="E9">
-        <v>17724</v>
+        <v>17916</v>
       </c>
       <c r="F9">
-        <v>1252</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G9">
-        <v>0.43639688737785798</v>
+        <v>0.31663227546399703</v>
       </c>
       <c r="H9">
-        <v>5.0896583277326002</v>
+        <v>6.2459704882807001</v>
       </c>
       <c r="I9">
-        <v>9.3211702577613201E-2</v>
+        <v>8.6233307127701997E-2</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>44963</v>
+        <v>44930</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -6785,27 +8002,27 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>20.67</v>
+        <v>22.6</v>
       </c>
       <c r="E10">
-        <v>17820</v>
+        <v>22074</v>
       </c>
       <c r="F10">
-        <v>1663</v>
+        <v>1652</v>
       </c>
       <c r="G10">
-        <v>0.49579255476263101</v>
+        <v>0.31948997437322302</v>
       </c>
       <c r="H10">
-        <v>1.70052389288857</v>
+        <v>6.3966655790962204</v>
       </c>
       <c r="I10">
-        <v>3.4896020226987699E-2</v>
+        <v>8.9702364013825406E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>44963</v>
+        <v>44930</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -6814,27 +8031,27 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>20.67</v>
+        <v>22.6</v>
       </c>
       <c r="E11">
-        <v>17430</v>
+        <v>21846</v>
       </c>
       <c r="F11">
-        <v>1639</v>
+        <v>1517</v>
       </c>
       <c r="G11">
-        <v>0.480629804545051</v>
+        <v>0.32111502024014399</v>
       </c>
       <c r="H11">
-        <v>1.75156963455646</v>
+        <v>6.32249939376835</v>
       </c>
       <c r="I11">
-        <v>3.4844261714816097E-2</v>
+        <v>8.91132790723521E-2</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>44979</v>
+        <v>44951</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -6843,24 +8060,27 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>22.52</v>
+        <v>21.12</v>
       </c>
       <c r="E12">
-        <v>20958</v>
+        <v>17724</v>
       </c>
       <c r="F12">
-        <v>2531</v>
+        <v>1252</v>
       </c>
       <c r="G12">
-        <v>1.0466739120111399</v>
+        <v>0.32813007464273403</v>
+      </c>
+      <c r="H12">
+        <v>6.7689956626427303</v>
       </c>
       <c r="I12">
-        <v>8.1762121162189602E-2</v>
+        <v>9.3211702577613201E-2</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>44993</v>
+        <v>44893</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -6869,27 +8089,24 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>22.46</v>
+        <v>21.26</v>
       </c>
       <c r="E13">
-        <v>23418</v>
+        <v>16596</v>
       </c>
       <c r="F13">
-        <v>2303</v>
+        <v>1514</v>
       </c>
       <c r="G13">
-        <v>0.79710907302071798</v>
-      </c>
-      <c r="H13">
-        <v>1.6852047257509399</v>
+        <v>0.342845759934436</v>
       </c>
       <c r="I13">
-        <v>5.8713241370284802E-2</v>
+        <v>0.32533250684668602</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>45021</v>
+        <v>45035</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -6898,27 +8115,27 @@
         <v>10</v>
       </c>
       <c r="D14">
-        <v>22.46</v>
+        <v>21.22</v>
       </c>
       <c r="E14">
-        <v>18738</v>
+        <v>18840</v>
       </c>
       <c r="F14">
-        <v>2250</v>
+        <v>1614</v>
       </c>
       <c r="G14">
-        <v>0.61655902950461705</v>
+        <v>0.40915209872903202</v>
       </c>
       <c r="H14">
-        <v>4.0380784985144702</v>
+        <v>6.0301251612138902</v>
       </c>
       <c r="I14">
-        <v>0.108821587164582</v>
+        <v>0.103858236820834</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>45035</v>
+        <v>44963</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -6927,27 +8144,27 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>21.22</v>
+        <v>20.67</v>
       </c>
       <c r="E15">
-        <v>18840</v>
+        <v>17820</v>
       </c>
       <c r="F15">
-        <v>1614</v>
+        <v>1663</v>
       </c>
       <c r="G15">
-        <v>0.441514938764208</v>
+        <v>0.44151648579325398</v>
       </c>
       <c r="H15">
-        <v>5.5881197864225403</v>
+        <v>1.9095710181134999</v>
       </c>
       <c r="I15">
-        <v>0.103858236820834</v>
+        <v>3.4896020226987699E-2</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>45049</v>
+        <v>44963</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -6956,27 +8173,27 @@
         <v>10</v>
       </c>
       <c r="D16">
-        <v>21.58</v>
+        <v>20.67</v>
       </c>
       <c r="E16">
-        <v>17832</v>
+        <v>17430</v>
       </c>
       <c r="F16">
-        <v>1433</v>
+        <v>1639</v>
       </c>
       <c r="G16">
-        <v>0.34602005466925301</v>
+        <v>0.44370136881571698</v>
       </c>
       <c r="H16">
-        <v>8.9343863614644494</v>
+        <v>1.8973495018753599</v>
       </c>
       <c r="I16">
-        <v>0.13157311940136501</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3.4844261714816097E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>45063</v>
+        <v>45021</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -6985,27 +8202,27 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>22.68</v>
+        <v>22.46</v>
       </c>
       <c r="E17">
-        <v>26088</v>
+        <v>18738</v>
       </c>
       <c r="F17">
-        <v>573.20000000000005</v>
+        <v>2250</v>
       </c>
       <c r="G17">
-        <v>0.27803049853348299</v>
+        <v>0.59685227693446097</v>
       </c>
       <c r="H17">
-        <v>8.2600141156089606</v>
+        <v>4.17140699017712</v>
       </c>
       <c r="I17">
-        <v>0.101043637751804</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.108821587164582</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>45076</v>
+        <v>44993</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -7014,27 +8231,27 @@
         <v>10</v>
       </c>
       <c r="D18">
-        <v>22.68</v>
+        <v>22.46</v>
       </c>
       <c r="E18">
-        <v>19452</v>
+        <v>23418</v>
       </c>
       <c r="F18">
-        <v>1103</v>
+        <v>2303</v>
       </c>
       <c r="G18">
-        <v>0.21894230032698</v>
+        <v>0.77273115566626005</v>
       </c>
       <c r="H18">
-        <v>13.1656779100593</v>
+        <v>1.7383691170511399</v>
       </c>
       <c r="I18">
-        <v>0.12682610302880001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>5.8713241370284802E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>45089</v>
+        <v>44979</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -7043,25 +8260,34 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>22.7</v>
+        <v>22.52</v>
       </c>
       <c r="E19">
-        <v>18408</v>
+        <v>20958</v>
       </c>
       <c r="F19">
-        <v>1260</v>
+        <v>2531</v>
       </c>
       <c r="G19">
-        <v>0.232917931310444</v>
+        <v>1.0455348823919599</v>
       </c>
       <c r="H19">
-        <v>6.6314029468288096</v>
+        <v>1.78592995957968</v>
       </c>
       <c r="I19">
-        <v>6.7999325636522806E-2</v>
+        <v>8.1762121162189602E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K29">
+        <f>AVERAGE(H2:H14)</f>
+        <v>7.1413809980494012</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I19">
+    <sortCondition ref="G2:G19"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
@@ -7070,7 +8296,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7104,7 +8330,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>44865</v>
+        <v>45063</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -7113,27 +8339,27 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>22.07</v>
+        <v>22.29</v>
       </c>
       <c r="E2">
-        <v>15906</v>
+        <v>27888</v>
       </c>
       <c r="F2">
-        <v>2886</v>
+        <v>2037</v>
       </c>
       <c r="G2">
-        <v>0.74444040347881602</v>
+        <v>0.73060288362784198</v>
       </c>
       <c r="H2">
-        <v>8.82249492952735</v>
+        <v>1.59154333122255</v>
       </c>
       <c r="I2">
-        <v>0.28371267800875299</v>
+        <v>5.0564073384387197E-2</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>44865</v>
+        <v>45063</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -7142,56 +8368,56 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <v>22.07</v>
+        <v>22.29</v>
       </c>
       <c r="E3">
-        <v>15702</v>
+        <v>27810</v>
       </c>
       <c r="F3">
-        <v>2895</v>
+        <v>2002</v>
       </c>
       <c r="G3">
-        <v>0.74708240544637805</v>
+        <v>0.73067292779711301</v>
       </c>
       <c r="H3">
-        <v>8.7973759606947599</v>
+        <v>1.58923907068933</v>
       </c>
       <c r="I3">
-        <v>0.28390892842010401</v>
+        <v>5.0495706600471001E-2</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>44865</v>
+        <v>45049</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>22.07</v>
+        <v>20.8</v>
       </c>
       <c r="E4">
-        <v>23988</v>
+        <v>23148</v>
       </c>
       <c r="F4">
-        <v>2895</v>
+        <v>1645</v>
       </c>
       <c r="G4">
-        <v>0.74708240544637805</v>
+        <v>0.73279435804070603</v>
       </c>
       <c r="H4">
-        <v>8.3860633239169893</v>
+        <v>1.7368096314749899</v>
       </c>
       <c r="I4">
-        <v>0.27063504647224101</v>
+        <v>5.28891795796579E-2</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>44879</v>
+        <v>44865</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -7199,28 +8425,28 @@
       <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" t="e">
-        <v>#NUM!</v>
+      <c r="D5">
+        <v>22.07</v>
       </c>
       <c r="E5">
-        <v>18930</v>
+        <v>15906</v>
       </c>
       <c r="F5">
-        <v>1620</v>
+        <v>2886</v>
       </c>
       <c r="G5">
-        <v>0.73595647098479799</v>
-      </c>
-      <c r="H5" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="I5" t="e">
-        <v>#NUM!</v>
+        <v>0.73980051064202401</v>
+      </c>
+      <c r="H5">
+        <v>8.8778279962626208</v>
+      </c>
+      <c r="I5">
+        <v>0.28371267800875299</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>44907</v>
+        <v>44865</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -7229,51 +8455,51 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>22.24</v>
+        <v>22.07</v>
       </c>
       <c r="E6">
-        <v>19422</v>
+        <v>15702</v>
       </c>
       <c r="F6">
-        <v>1485</v>
+        <v>2895</v>
       </c>
       <c r="G6">
-        <v>0.74135857648333003</v>
+        <v>0.73988407796505096</v>
       </c>
       <c r="H6">
-        <v>0.546156053502313</v>
+        <v>8.8829655753754899</v>
       </c>
       <c r="I6">
-        <v>1.7580546593506E-2</v>
+        <v>0.28390892842010401</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>44907</v>
+        <v>44865</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>22.24</v>
+        <v>22.07</v>
       </c>
       <c r="E7">
-        <v>19224</v>
+        <v>23988</v>
       </c>
       <c r="F7">
-        <v>1494</v>
+        <v>2895</v>
       </c>
       <c r="G7">
-        <v>0.73801102231512195</v>
+        <v>0.73988407796505096</v>
       </c>
       <c r="H7">
-        <v>0.54890878848361302</v>
+        <v>8.4676512805746391</v>
       </c>
       <c r="I7">
-        <v>1.75893721691051E-2</v>
+        <v>0.27063504647224101</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -7284,53 +8510,59 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>22.24</v>
       </c>
       <c r="E8">
-        <v>23310</v>
+        <v>19224</v>
       </c>
       <c r="F8">
         <v>1494</v>
       </c>
       <c r="G8">
-        <v>0.73801102231512195</v>
+        <v>0.74079475097583203</v>
       </c>
       <c r="H8">
-        <v>0.60116621714977203</v>
+        <v>0.54684612115962805</v>
       </c>
       <c r="I8">
-        <v>1.92639224417448E-2</v>
+        <v>1.75893721691051E-2</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>44951</v>
+        <v>44907</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9">
-        <v>20.14</v>
+        <v>22.24</v>
       </c>
       <c r="E9">
-        <v>22920</v>
+        <v>23310</v>
       </c>
       <c r="F9">
-        <v>1341</v>
+        <v>1494</v>
+      </c>
+      <c r="G9">
+        <v>0.74079475097583203</v>
+      </c>
+      <c r="H9">
+        <v>0.59890717896635304</v>
       </c>
       <c r="I9">
-        <v>0.126013828102645</v>
+        <v>1.92639224417448E-2</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>44963</v>
+        <v>44907</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -7339,56 +8571,56 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>16.440000000000001</v>
+        <v>22.24</v>
       </c>
       <c r="E10">
-        <v>17790</v>
+        <v>19422</v>
       </c>
       <c r="F10">
-        <v>573.20000000000005</v>
+        <v>1485</v>
       </c>
       <c r="G10">
-        <v>0.94013690659964499</v>
+        <v>0.74090071769494803</v>
       </c>
       <c r="H10">
-        <v>0.87780109294661901</v>
+        <v>0.54649356478142497</v>
       </c>
       <c r="I10">
-        <v>2.9859393205386602E-2</v>
+        <v>1.7580546593506E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>44963</v>
+        <v>44879</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11">
-        <v>16.440000000000001</v>
+        <v>10</v>
+      </c>
+      <c r="D11" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E11">
-        <v>16608</v>
+        <v>18930</v>
       </c>
       <c r="F11">
-        <v>573.20000000000005</v>
+        <v>1620</v>
       </c>
       <c r="G11">
-        <v>0.94013690659964499</v>
-      </c>
-      <c r="H11">
-        <v>1.4519839738386</v>
-      </c>
-      <c r="I11">
-        <v>4.93908708375271E-2</v>
+        <v>0.74132115970993895</v>
+      </c>
+      <c r="H11" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I11" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>44979</v>
+        <v>44951</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -7397,27 +8629,27 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>16.37</v>
+        <v>20.14</v>
       </c>
       <c r="E12">
-        <v>20574</v>
+        <v>21786</v>
       </c>
       <c r="F12">
-        <v>573.20000000000005</v>
+        <v>1266</v>
       </c>
       <c r="G12">
-        <v>1.6365523626110301</v>
+        <v>0.74252870479035604</v>
       </c>
       <c r="H12">
-        <v>5.0888703183105299</v>
+        <v>4.1536506647998497</v>
       </c>
       <c r="I12">
-        <v>0.300642041521472</v>
+        <v>0.12557737123057999</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>44979</v>
+        <v>44951</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -7426,27 +8658,27 @@
         <v>11</v>
       </c>
       <c r="D13">
-        <v>16.37</v>
+        <v>20.14</v>
       </c>
       <c r="E13">
-        <v>24666</v>
+        <v>19104</v>
       </c>
       <c r="F13">
-        <v>573.20000000000005</v>
+        <v>1266</v>
       </c>
       <c r="G13">
-        <v>1.6365503262844301</v>
+        <v>0.74252870479035604</v>
       </c>
       <c r="H13">
-        <v>2.40077248915492</v>
+        <v>1.5709301178400801</v>
       </c>
       <c r="I13">
-        <v>0.14183349135158899</v>
+        <v>4.7493949420709801E-2</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>44993</v>
+        <v>44951</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -7455,56 +8687,56 @@
         <v>10</v>
       </c>
       <c r="D14">
-        <v>22.02</v>
+        <v>20.14</v>
       </c>
       <c r="E14">
-        <v>25266</v>
+        <v>22920</v>
       </c>
       <c r="F14">
-        <v>2432</v>
+        <v>1341</v>
       </c>
       <c r="G14">
-        <v>1.30448070052289</v>
+        <v>0.74281434911411404</v>
       </c>
       <c r="H14">
-        <v>1.9306644615616699</v>
+        <v>4.1664842881561501</v>
       </c>
       <c r="I14">
-        <v>0.108628810801549</v>
+        <v>0.126013828102645</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>44993</v>
+        <v>45035</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15">
-        <v>22.02</v>
+        <v>20.88</v>
       </c>
       <c r="E15">
-        <v>16998</v>
+        <v>21378</v>
       </c>
       <c r="F15">
-        <v>2432</v>
+        <v>1167</v>
       </c>
       <c r="G15">
-        <v>1.30448070052289</v>
+        <v>0.82876864696313601</v>
       </c>
       <c r="H15">
-        <v>1.86173816210085</v>
+        <v>2.1882598556347701</v>
       </c>
       <c r="I15">
-        <v>0.104750673459483</v>
+        <v>7.5549822496813093E-2</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>45021</v>
+        <v>44963</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -7513,27 +8745,27 @@
         <v>10</v>
       </c>
       <c r="D16">
-        <v>22.34</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="E16">
-        <v>20658</v>
+        <v>17790</v>
       </c>
       <c r="F16">
-        <v>1695</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G16">
-        <v>1.0737458530561601</v>
+        <v>0.89351335106295304</v>
       </c>
       <c r="H16">
-        <v>1.59092321795575</v>
+        <v>0.92360478234698296</v>
       </c>
       <c r="I16">
-        <v>7.4395623684086906E-2</v>
+        <v>2.9859393205386602E-2</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>45035</v>
+        <v>44963</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -7542,56 +8774,56 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>20.88</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="E17">
-        <v>21378</v>
+        <v>17430</v>
       </c>
       <c r="F17">
-        <v>1167</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G17">
-        <v>0.87112822010513902</v>
+        <v>0.89625197176154203</v>
       </c>
       <c r="H17">
-        <v>2.0818533000105202</v>
+        <v>0.920782581387938</v>
       </c>
       <c r="I17">
-        <v>7.5549822496813093E-2</v>
+        <v>2.9859393205386602E-2</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>45049</v>
+        <v>44963</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18">
-        <v>20.8</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="E18">
-        <v>23148</v>
+        <v>16608</v>
       </c>
       <c r="F18">
-        <v>1645</v>
+        <v>573.20000000000005</v>
       </c>
       <c r="G18">
-        <v>0.74034148245120202</v>
+        <v>0.89625197176154203</v>
       </c>
       <c r="H18">
-        <v>1.71910439858341</v>
+        <v>1.52308029952103</v>
       </c>
       <c r="I18">
-        <v>5.28891795796579E-2</v>
+        <v>4.93908708375271E-2</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>45063</v>
+        <v>45021</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -7600,27 +8832,27 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>22.29</v>
+        <v>22.34</v>
       </c>
       <c r="E19">
-        <v>27888</v>
+        <v>20658</v>
       </c>
       <c r="F19">
-        <v>2037</v>
+        <v>1695</v>
       </c>
       <c r="G19">
-        <v>0.73548915823757399</v>
+        <v>1.0582857713989</v>
       </c>
       <c r="H19">
-        <v>1.58096979974008</v>
+        <v>1.6141643911102601</v>
       </c>
       <c r="I19">
-        <v>5.0564073384387197E-2</v>
+        <v>7.4395623684086906E-2</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>45063</v>
+        <v>44993</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -7629,26 +8861,117 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>22.29</v>
+        <v>22.02</v>
       </c>
       <c r="E20">
-        <v>27810</v>
+        <v>25266</v>
       </c>
       <c r="F20">
-        <v>2002</v>
+        <v>2432</v>
       </c>
       <c r="G20">
-        <v>0.73478767869014106</v>
+        <v>1.29844388483991</v>
       </c>
       <c r="H20">
-        <v>1.5803394618975599</v>
+        <v>1.9396406411534199</v>
       </c>
       <c r="I20">
-        <v>5.0495706600471001E-2</v>
+        <v>0.108628810801549</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>44993</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>22.02</v>
+      </c>
+      <c r="E21">
+        <v>16998</v>
+      </c>
+      <c r="F21">
+        <v>2432</v>
+      </c>
+      <c r="G21">
+        <v>1.29844388483991</v>
+      </c>
+      <c r="H21">
+        <v>1.87039388474377</v>
+      </c>
+      <c r="I21">
+        <v>0.104750673459483</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>44979</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <v>16.37</v>
+      </c>
+      <c r="E22">
+        <v>20574</v>
+      </c>
+      <c r="F22">
+        <v>573.20000000000005</v>
+      </c>
+      <c r="G22">
+        <v>1.63794044253354</v>
+      </c>
+      <c r="H22">
+        <v>5.0845577324962603</v>
+      </c>
+      <c r="I22">
+        <v>0.300642041521472</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>44979</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>16.37</v>
+      </c>
+      <c r="E23">
+        <v>24666</v>
+      </c>
+      <c r="F23">
+        <v>573.20000000000005</v>
+      </c>
+      <c r="G23">
+        <v>1.63944889300297</v>
+      </c>
+      <c r="H23">
+        <v>2.3965278925312901</v>
+      </c>
+      <c r="I23">
+        <v>0.14183349135158899</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I23">
+    <sortCondition ref="G2:G23"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/04_Outputs/rC_k600.xlsx
+++ b/04_Outputs/rC_k600.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samanthahowley\Desktop\SpringMetabolism_FlowReversals\04_Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\04_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E64B721-29C4-4F01-8ABC-28F8353ED5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CC57A7-41C1-4CB4-8353-D853BDC75ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AM" sheetId="1" r:id="rId1"/>
@@ -231,6 +231,20 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>AM!$G$2:$G$33</c:f>
@@ -345,9 +359,6 @@
                 <c:pt idx="0">
                   <c:v>21.369670657725798</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.0246525978349297</c:v>
-                </c:pt>
                 <c:pt idx="4">
                   <c:v>13.892989272610601</c:v>
                 </c:pt>
@@ -363,24 +374,12 @@
                 <c:pt idx="8">
                   <c:v>20.582320358999102</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>9.9111329260555596</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>10.1577577965675</c:v>
-                </c:pt>
                 <c:pt idx="13">
                   <c:v>25.708252717455</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>25.6620546637158</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>6.9745538382867203</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6.9616991075446499</c:v>
-                </c:pt>
                 <c:pt idx="17">
                   <c:v>16.279117207498601</c:v>
                 </c:pt>
@@ -393,9 +392,6 @@
                 <c:pt idx="20">
                   <c:v>10.726642441441401</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>6.8424673213972902</c:v>
-                </c:pt>
                 <c:pt idx="22">
                   <c:v>2.1574183462267702</c:v>
                 </c:pt>
@@ -419,12 +415,6 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>1.36490590126142</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.45773182901047699</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.58021307026655</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -805,15 +795,6 @@
                 <c:pt idx="2">
                   <c:v>10.818929035817799</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>16.7661132110034</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>16.818242674381999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>16.428025299675401</c:v>
-                </c:pt>
                 <c:pt idx="6">
                   <c:v>9.6476919720071006</c:v>
                 </c:pt>
@@ -1139,6 +1120,20 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>ID!$G$2:$G$16</c:f>
@@ -1226,20 +1221,11 @@
                 <c:pt idx="8">
                   <c:v>2.1878451594958102</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>6.3531601948909397</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>6.3151101233337998</c:v>
-                </c:pt>
                 <c:pt idx="11">
                   <c:v>3.8892751359493398</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>2.3123306997931201</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>4.1959327736538397</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>1.01033184827849</c:v>
@@ -1527,6 +1513,20 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>LF!$G$2:$G$19</c:f>
@@ -1626,20 +1626,11 @@
                 <c:pt idx="12">
                   <c:v>6.0301251612138902</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.9095710181134999</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.8973495018753599</c:v>
-                </c:pt>
                 <c:pt idx="15">
                   <c:v>4.17140699017712</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>1.7383691170511399</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1.78592995957968</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5176,15 +5167,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>182562</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5533,9 +5524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O33"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5564,7 +5555,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A2" s="1">
         <v>45064</v>
       </c>
@@ -5593,7 +5584,7 @@
         <v>0.21888147684550499</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A3" s="1">
         <v>45086</v>
       </c>
@@ -5619,7 +5610,7 @@
         <v>0.458224391330884</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A4" s="1">
         <v>45086</v>
       </c>
@@ -5645,7 +5636,7 @@
         <v>0.72834929859255104</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A5" s="1">
         <v>44929</v>
       </c>
@@ -5667,14 +5658,11 @@
       <c r="G5">
         <v>0.256226733839999</v>
       </c>
-      <c r="H5">
-        <v>6.0246525978349297</v>
-      </c>
       <c r="I5">
         <v>6.5658835581262703E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A6" s="1">
         <v>44929</v>
       </c>
@@ -5703,7 +5691,7 @@
         <v>0.15141080478406299</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A7" s="1">
         <v>44914</v>
       </c>
@@ -5732,7 +5720,7 @@
         <v>0.21232712840356199</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A8" s="1">
         <v>44914</v>
       </c>
@@ -5761,7 +5749,7 @@
         <v>0.23365658256366301</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A9" s="1">
         <v>44900</v>
       </c>
@@ -5790,7 +5778,7 @@
         <v>0.22984039458512301</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A10" s="1">
         <v>44900</v>
       </c>
@@ -5819,7 +5807,7 @@
         <v>0.22765704934814299</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A11" s="1">
         <v>44886</v>
       </c>
@@ -5841,14 +5829,11 @@
       <c r="G11">
         <v>0.26494909806747902</v>
       </c>
-      <c r="H11">
-        <v>9.9111329260555596</v>
-      </c>
       <c r="I11">
         <v>0.111250452341418</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A12" s="1">
         <v>44886</v>
       </c>
@@ -5874,7 +5859,7 @@
         <v>0.427275897045924</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A13" s="1">
         <v>44886</v>
       </c>
@@ -5896,14 +5881,11 @@
       <c r="G13">
         <v>0.26502797555140301</v>
       </c>
-      <c r="H13">
-        <v>10.1577577965675</v>
-      </c>
       <c r="I13">
         <v>0.114052710685128</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A14" s="1">
         <v>44872</v>
       </c>
@@ -5926,7 +5908,7 @@
         <v>0.26658216225721099</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A15" s="1">
         <v>45050</v>
       </c>
@@ -5955,7 +5937,7 @@
         <v>0.36364535366281198</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A16" s="1">
         <v>45050</v>
       </c>
@@ -5984,7 +5966,7 @@
         <v>0.364586830306599</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A17" s="1">
         <v>45042</v>
       </c>
@@ -6006,14 +5988,11 @@
       <c r="G17">
         <v>0.35825069383838998</v>
       </c>
-      <c r="H17">
-        <v>6.9745538382867203</v>
-      </c>
       <c r="I17">
         <v>0.10653628208794499</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A18" s="1">
         <v>45042</v>
       </c>
@@ -6035,14 +6014,11 @@
       <c r="G18">
         <v>0.35891220134342799</v>
       </c>
-      <c r="H18">
-        <v>6.9616991075446499</v>
-      </c>
       <c r="I18">
         <v>0.10653628208794499</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A19" s="1">
         <v>44944</v>
       </c>
@@ -6071,7 +6047,7 @@
         <v>0.24930788677166099</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A20" s="1">
         <v>44944</v>
       </c>
@@ -6100,7 +6076,7 @@
         <v>0.322399708046537</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A21" s="1">
         <v>44944</v>
       </c>
@@ -6130,10 +6106,10 @@
       </c>
       <c r="K21">
         <f>AVERAGE(H2:H23)</f>
-        <v>15.699331506482597</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>19.642975294083342</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A22" s="1">
         <v>45075</v>
       </c>
@@ -6162,7 +6138,7 @@
         <v>0.18671246119286999</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A23" s="1">
         <v>45075</v>
       </c>
@@ -6184,14 +6160,11 @@
       <c r="G23">
         <v>0.41065339316936</v>
       </c>
-      <c r="H23">
-        <v>6.8424673213972902</v>
-      </c>
       <c r="I23">
         <v>0.119261080090433</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A24" s="1">
         <v>45028</v>
       </c>
@@ -6220,7 +6193,7 @@
         <v>6.6607504518364599E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A25" s="1">
         <v>45028</v>
       </c>
@@ -6249,7 +6222,7 @@
         <v>0.168634803961631</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A26" s="1">
         <v>45028</v>
       </c>
@@ -6278,7 +6251,7 @@
         <v>6.6480777911594499E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A27" s="1">
         <v>45014</v>
       </c>
@@ -6307,7 +6280,7 @@
         <v>0.104238501087662</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A28" s="1">
         <v>45014</v>
       </c>
@@ -6336,7 +6309,7 @@
         <v>7.8285122388467202E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A29" s="1">
         <v>45014</v>
       </c>
@@ -6365,7 +6338,7 @@
         <v>7.7870915391702794E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A30" s="1">
         <v>44958</v>
       </c>
@@ -6397,7 +6370,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A31" s="1">
         <v>44958</v>
       </c>
@@ -6426,7 +6399,7 @@
         <v>5.4167358095754702E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A32" s="1">
         <v>44972</v>
       </c>
@@ -6448,14 +6421,11 @@
       <c r="G32">
         <v>1.60103975950207</v>
       </c>
-      <c r="H32">
-        <v>0.45773182901047699</v>
-      </c>
       <c r="I32">
         <v>2.4799278587846699E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A33" s="1">
         <v>44972</v>
       </c>
@@ -6476,9 +6446,6 @@
       </c>
       <c r="G33">
         <v>1.60103975950207</v>
-      </c>
-      <c r="H33">
-        <v>0.58021307026655</v>
       </c>
       <c r="I33">
         <v>3.14351431512985E-2</v>
@@ -6497,9 +6464,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6528,7 +6495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A2" s="1">
         <v>45064</v>
       </c>
@@ -6557,7 +6524,7 @@
         <v>0.175804478721235</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A3" s="1">
         <v>45064</v>
       </c>
@@ -6586,7 +6553,7 @@
         <v>0.174084658920136</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A4" s="1">
         <v>45075</v>
       </c>
@@ -6615,7 +6582,7 @@
         <v>0.194662682442417</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A5" s="1">
         <v>45042</v>
       </c>
@@ -6637,14 +6604,11 @@
       <c r="G5">
         <v>0.41420772624117003</v>
       </c>
-      <c r="H5">
-        <v>16.7661132110034</v>
-      </c>
       <c r="I5">
         <v>0.30208121634153201</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A6" s="1">
         <v>45042</v>
       </c>
@@ -6666,14 +6630,11 @@
       <c r="G6">
         <v>0.41427437299901998</v>
       </c>
-      <c r="H6">
-        <v>16.818242674381999</v>
-      </c>
       <c r="I6">
         <v>0.30306920854747199</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A7" s="1">
         <v>45028</v>
       </c>
@@ -6695,14 +6656,11 @@
       <c r="G7">
         <v>0.437729121568594</v>
       </c>
-      <c r="H7">
-        <v>16.428025299675401</v>
-      </c>
       <c r="I7">
         <v>0.27017532655438897</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A8" s="1">
         <v>44972</v>
       </c>
@@ -6731,7 +6689,7 @@
         <v>0.19102312806001301</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A9" s="1">
         <v>44972</v>
       </c>
@@ -6760,7 +6718,7 @@
         <v>0.19010186714109101</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A10" s="1">
         <v>44972</v>
       </c>
@@ -6789,7 +6747,7 @@
         <v>0.16502092939104501</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A11" s="1">
         <v>45000</v>
       </c>
@@ -6818,7 +6776,7 @@
         <v>0.151048107990056</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A12" s="1">
         <v>45000</v>
       </c>
@@ -6847,7 +6805,7 @@
         <v>0.15037633463830899</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A13" s="1">
         <v>44958</v>
       </c>
@@ -6876,7 +6834,7 @@
         <v>0.16929271518545699</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A14" s="1">
         <v>44958</v>
       </c>
@@ -6905,7 +6863,7 @@
         <v>0.20150573574547101</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A15" s="1">
         <v>44929</v>
       </c>
@@ -6934,7 +6892,7 @@
         <v>8.5824373596079695E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A16" s="1">
         <v>44929</v>
       </c>
@@ -6963,7 +6921,7 @@
         <v>8.5265157298292205E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A17" s="1">
         <v>44929</v>
       </c>
@@ -6992,7 +6950,7 @@
         <v>0.22389103675868699</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A18" s="1">
         <v>44944</v>
       </c>
@@ -7021,7 +6979,7 @@
         <v>0.126907453227872</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A19" s="1">
         <v>44944</v>
       </c>
@@ -7050,7 +7008,7 @@
         <v>0.124889895165891</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A20" s="1">
         <v>44915</v>
       </c>
@@ -7079,7 +7037,7 @@
         <v>7.5136667138173505E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A21" s="1">
         <v>44900</v>
       </c>
@@ -7108,7 +7066,7 @@
         <v>0.20549062678525201</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A22" s="1">
         <v>44872</v>
       </c>
@@ -7134,7 +7092,7 @@
         <v>0.59945886197372</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A23" s="1">
         <v>44886</v>
       </c>
@@ -7160,7 +7118,7 @@
         <v>0.53111765810454403</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A24" s="1">
         <v>44886</v>
       </c>
@@ -7187,10 +7145,10 @@
       </c>
       <c r="K24">
         <f>AVERAGE(H2:H21)</f>
-        <v>9.2396615479724069</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7.9282852808463131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A25" s="1">
         <v>44858</v>
       </c>
@@ -7213,7 +7171,7 @@
         <v>0.56969572112081401</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A26" s="1">
         <v>44986</v>
       </c>
@@ -7249,9 +7207,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7280,7 +7238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A2" s="1">
         <v>44929</v>
       </c>
@@ -7309,7 +7267,7 @@
         <v>0.119445760939699</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A3" s="1">
         <v>45075</v>
       </c>
@@ -7338,7 +7296,7 @@
         <v>0.20696150256924101</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A4" s="1">
         <v>44914</v>
       </c>
@@ -7367,7 +7325,7 @@
         <v>0.129380530943568</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A5" s="1">
         <v>44944</v>
       </c>
@@ -7396,7 +7354,7 @@
         <v>0.117028118053404</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A6" s="1">
         <v>44900</v>
       </c>
@@ -7425,7 +7383,7 @@
         <v>0.12917745061024599</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A7" s="1">
         <v>44886</v>
       </c>
@@ -7454,7 +7412,7 @@
         <v>0.30021111601335398</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A8" s="1">
         <v>44872</v>
       </c>
@@ -7483,7 +7441,7 @@
         <v>0.15855698156709899</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A9" s="1">
         <v>45042</v>
       </c>
@@ -7512,7 +7470,7 @@
         <v>0.203481011201437</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A10" s="1">
         <v>44958</v>
       </c>
@@ -7541,7 +7499,7 @@
         <v>0.113686385875942</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A11" s="1">
         <v>45028</v>
       </c>
@@ -7563,14 +7521,11 @@
       <c r="G11">
         <v>1.4229669796427999</v>
       </c>
-      <c r="H11">
-        <v>6.3531601948909397</v>
-      </c>
       <c r="I11">
         <v>0.37683641747636698</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A12" s="1">
         <v>45028</v>
       </c>
@@ -7592,14 +7547,11 @@
       <c r="G12">
         <v>1.4304669796428</v>
       </c>
-      <c r="H12">
-        <v>6.3151101233337998</v>
-      </c>
       <c r="I12">
         <v>0.37655377279801899</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A13" s="1">
         <v>45014</v>
       </c>
@@ -7628,7 +7580,7 @@
         <v>0.26715501908250799</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A14" s="1">
         <v>45000</v>
       </c>
@@ -7657,7 +7609,7 @@
         <v>0.15994316366882999</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A15" s="1">
         <v>44972</v>
       </c>
@@ -7679,14 +7631,11 @@
       <c r="G15">
         <v>1.85747687368365</v>
       </c>
-      <c r="H15">
-        <v>4.1959327736538397</v>
-      </c>
       <c r="I15">
         <v>0.31615444563082801</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A16" s="1">
         <v>44986</v>
       </c>
@@ -7715,10 +7664,10 @@
         <v>0.104012943753354</v>
       </c>
     </row>
-    <row r="19" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="11:11" x14ac:dyDescent="0.75">
       <c r="K19">
         <f>AVERAGE(H2:H12)</f>
-        <v>4.4493221044370239</v>
+        <v>4.0304747589536127</v>
       </c>
     </row>
   </sheetData>
@@ -7734,9 +7683,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7765,7 +7714,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A2" s="1">
         <v>44937</v>
       </c>
@@ -7791,7 +7740,7 @@
         <v>0.260812263010191</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A3" s="1">
         <v>44907</v>
       </c>
@@ -7820,7 +7769,7 @@
         <v>7.5485220817124901E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A4" s="1">
         <v>44879</v>
       </c>
@@ -7846,7 +7795,7 @@
         <v>0.28993461685199901</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A5" s="1">
         <v>45076</v>
       </c>
@@ -7875,7 +7824,7 @@
         <v>0.12682610302880001</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A6" s="1">
         <v>45089</v>
       </c>
@@ -7904,7 +7853,7 @@
         <v>6.7999325636522806E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A7" s="1">
         <v>45063</v>
       </c>
@@ -7933,7 +7882,7 @@
         <v>0.101043637751804</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A8" s="1">
         <v>45049</v>
       </c>
@@ -7962,7 +7911,7 @@
         <v>0.13157311940136501</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A9" s="1">
         <v>44865</v>
       </c>
@@ -7991,7 +7940,7 @@
         <v>8.6233307127701997E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A10" s="1">
         <v>44930</v>
       </c>
@@ -8020,7 +7969,7 @@
         <v>8.9702364013825406E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A11" s="1">
         <v>44930</v>
       </c>
@@ -8049,7 +7998,7 @@
         <v>8.91132790723521E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A12" s="1">
         <v>44951</v>
       </c>
@@ -8078,7 +8027,7 @@
         <v>9.3211702577613201E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A13" s="1">
         <v>44893</v>
       </c>
@@ -8104,7 +8053,7 @@
         <v>0.32533250684668602</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A14" s="1">
         <v>45035</v>
       </c>
@@ -8133,7 +8082,7 @@
         <v>0.103858236820834</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A15" s="1">
         <v>44963</v>
       </c>
@@ -8155,14 +8104,11 @@
       <c r="G15">
         <v>0.44151648579325398</v>
       </c>
-      <c r="H15">
-        <v>1.9095710181134999</v>
-      </c>
       <c r="I15">
         <v>3.4896020226987699E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A16" s="1">
         <v>44963</v>
       </c>
@@ -8184,14 +8130,11 @@
       <c r="G16">
         <v>0.44370136881571698</v>
       </c>
-      <c r="H16">
-        <v>1.8973495018753599</v>
-      </c>
       <c r="I16">
         <v>3.4844261714816097E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A17" s="1">
         <v>45021</v>
       </c>
@@ -8220,7 +8163,7 @@
         <v>0.108821587164582</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A18" s="1">
         <v>44993</v>
       </c>
@@ -8249,7 +8192,7 @@
         <v>5.8713241370284802E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A19" s="1">
         <v>44979</v>
       </c>
@@ -8271,14 +8214,11 @@
       <c r="G19">
         <v>1.0455348823919599</v>
       </c>
-      <c r="H19">
-        <v>1.78592995957968</v>
-      </c>
       <c r="I19">
         <v>8.1762121162189602E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.75">
       <c r="K29">
         <f>AVERAGE(H2:H14)</f>
         <v>7.1413809980494012</v>
@@ -8297,9 +8237,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8328,7 +8268,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A2" s="1">
         <v>45063</v>
       </c>
@@ -8357,7 +8297,7 @@
         <v>5.0564073384387197E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A3" s="1">
         <v>45063</v>
       </c>
@@ -8386,7 +8326,7 @@
         <v>5.0495706600471001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A4" s="1">
         <v>45049</v>
       </c>
@@ -8415,7 +8355,7 @@
         <v>5.28891795796579E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A5" s="1">
         <v>44865</v>
       </c>
@@ -8444,7 +8384,7 @@
         <v>0.28371267800875299</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A6" s="1">
         <v>44865</v>
       </c>
@@ -8473,7 +8413,7 @@
         <v>0.28390892842010401</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A7" s="1">
         <v>44865</v>
       </c>
@@ -8502,7 +8442,7 @@
         <v>0.27063504647224101</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A8" s="1">
         <v>44907</v>
       </c>
@@ -8531,7 +8471,7 @@
         <v>1.75893721691051E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A9" s="1">
         <v>44907</v>
       </c>
@@ -8560,7 +8500,7 @@
         <v>1.92639224417448E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A10" s="1">
         <v>44907</v>
       </c>
@@ -8589,7 +8529,7 @@
         <v>1.7580546593506E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A11" s="1">
         <v>44879</v>
       </c>
@@ -8618,7 +8558,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A12" s="1">
         <v>44951</v>
       </c>
@@ -8647,7 +8587,7 @@
         <v>0.12557737123057999</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A13" s="1">
         <v>44951</v>
       </c>
@@ -8676,7 +8616,7 @@
         <v>4.7493949420709801E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A14" s="1">
         <v>44951</v>
       </c>
@@ -8705,7 +8645,7 @@
         <v>0.126013828102645</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A15" s="1">
         <v>45035</v>
       </c>
@@ -8734,7 +8674,7 @@
         <v>7.5549822496813093E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A16" s="1">
         <v>44963</v>
       </c>
@@ -8763,7 +8703,7 @@
         <v>2.9859393205386602E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A17" s="1">
         <v>44963</v>
       </c>
@@ -8792,7 +8732,7 @@
         <v>2.9859393205386602E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A18" s="1">
         <v>44963</v>
       </c>
@@ -8821,7 +8761,7 @@
         <v>4.93908708375271E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A19" s="1">
         <v>45021</v>
       </c>
@@ -8850,7 +8790,7 @@
         <v>7.4395623684086906E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A20" s="1">
         <v>44993</v>
       </c>
@@ -8879,7 +8819,7 @@
         <v>0.108628810801549</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A21" s="1">
         <v>44993</v>
       </c>
@@ -8908,7 +8848,7 @@
         <v>0.104750673459483</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A22" s="1">
         <v>44979</v>
       </c>
@@ -8937,7 +8877,7 @@
         <v>0.300642041521472</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A23" s="1">
         <v>44979</v>
       </c>
